--- a/R/data/quiz_250303.xlsx
+++ b/R/data/quiz_250303.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="656">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -1694,6 +1694,291 @@
   </si>
   <si>
     <t>김태호</t>
+  </si>
+  <si>
+    <t>jehun0@naver.com</t>
+  </si>
+  <si>
+    <t>이제훈</t>
+  </si>
+  <si>
+    <t>astpqls3541@naver.com</t>
+  </si>
+  <si>
+    <t>이세빈</t>
+  </si>
+  <si>
+    <t>tyn47760@gmail.com</t>
+  </si>
+  <si>
+    <t>권태연</t>
+  </si>
+  <si>
+    <t>pyjn1475@naver.com</t>
+  </si>
+  <si>
+    <t>박용준</t>
+  </si>
+  <si>
+    <t>yongjun9194@naver.com</t>
+  </si>
+  <si>
+    <t>소프트웨어학부 빅데이터학과</t>
+  </si>
+  <si>
+    <t>안용준</t>
+  </si>
+  <si>
+    <t>kty0305@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>김태윤</t>
+  </si>
+  <si>
+    <t>sion020821@daum.net</t>
+  </si>
+  <si>
+    <t>한림대학교</t>
+  </si>
+  <si>
+    <t>swl0427@naver.com</t>
+  </si>
+  <si>
+    <t>이승우</t>
+  </si>
+  <si>
+    <t>leedahoon12@naver.com</t>
+  </si>
+  <si>
+    <t>이다훈</t>
+  </si>
+  <si>
+    <t>brianbrian317@daum.net</t>
+  </si>
+  <si>
+    <t>김보성</t>
+  </si>
+  <si>
+    <t>yangkyung04@naver.com</t>
+  </si>
+  <si>
+    <t>양경호</t>
+  </si>
+  <si>
+    <t>dnjstkd458@naver.com</t>
+  </si>
+  <si>
+    <t>이원상</t>
+  </si>
+  <si>
+    <t>jjano01@naver.com</t>
+  </si>
+  <si>
+    <t>박찬호</t>
+  </si>
+  <si>
+    <t>angkscmzndyal@naver.com</t>
+  </si>
+  <si>
+    <t>박상재</t>
+  </si>
+  <si>
+    <t>kimjisung00120@gmail.com</t>
+  </si>
+  <si>
+    <t>정보과학대학보과학대학</t>
+  </si>
+  <si>
+    <t>김지성</t>
+  </si>
+  <si>
+    <t>yuvin0612@naver.com</t>
+  </si>
+  <si>
+    <t>장유빈</t>
+  </si>
+  <si>
+    <t>ksj040202@gmail.com</t>
+  </si>
+  <si>
+    <t>권수정</t>
+  </si>
+  <si>
+    <t>jjongwoo0628@naver.com</t>
+  </si>
+  <si>
+    <t>윤종우</t>
+  </si>
+  <si>
+    <t>ssuwan5@gmail.com</t>
+  </si>
+  <si>
+    <t>신수완</t>
+  </si>
+  <si>
+    <t>juicee220@gmail.com</t>
+  </si>
+  <si>
+    <t>최주아</t>
+  </si>
+  <si>
+    <t>jbh7574@naver.com</t>
+  </si>
+  <si>
+    <t>데이터테크</t>
+  </si>
+  <si>
+    <t>전병훈</t>
+  </si>
+  <si>
+    <t>gmltjd050406@gmail.com</t>
+  </si>
+  <si>
+    <t>김희성</t>
+  </si>
+  <si>
+    <t>won03336@gmail.com</t>
+  </si>
+  <si>
+    <t>소원</t>
+  </si>
+  <si>
+    <t>csb5042@hanmail.net</t>
+  </si>
+  <si>
+    <t>최수빈</t>
+  </si>
+  <si>
+    <t>jiwon020522@naver.com</t>
+  </si>
+  <si>
+    <t>박지원</t>
+  </si>
+  <si>
+    <t>wlgprnjs98@gmail.com</t>
+  </si>
+  <si>
+    <t>권지혜</t>
+  </si>
+  <si>
+    <t>mhk02083@naver.com</t>
+  </si>
+  <si>
+    <t>명희경</t>
+  </si>
+  <si>
+    <t>jhwoo0513@naver.com</t>
+  </si>
+  <si>
+    <t>사학전공</t>
+  </si>
+  <si>
+    <t>우재홍</t>
+  </si>
+  <si>
+    <t>dltmdrb7013@gmail.com</t>
+  </si>
+  <si>
+    <t>이승규</t>
+  </si>
+  <si>
+    <t>gtar7155@gmail.com</t>
+  </si>
+  <si>
+    <t>정민서</t>
+  </si>
+  <si>
+    <t>dlwntkd3526@naver.com</t>
+  </si>
+  <si>
+    <t>이주상</t>
+  </si>
+  <si>
+    <t>jeonguijin45@gmail.com</t>
+  </si>
+  <si>
+    <t>데이터사이언스학과</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정의진 </t>
+  </si>
+  <si>
+    <t>zosel1595@naver.com</t>
+  </si>
+  <si>
+    <t>소프트웨어융합학부 콘텐츠IT전공</t>
+  </si>
+  <si>
+    <t>최성민</t>
+  </si>
+  <si>
+    <t>seoyebbb@gmail.com</t>
+  </si>
+  <si>
+    <t>박서예</t>
+  </si>
+  <si>
+    <t>khw0316ee@gmail.com</t>
+  </si>
+  <si>
+    <t>김소정</t>
+  </si>
+  <si>
+    <t>kheom20113843@gmail.com</t>
+  </si>
+  <si>
+    <t>엄규현</t>
+  </si>
+  <si>
+    <t>yeup2004@gmail.com</t>
+  </si>
+  <si>
+    <t>경영대학</t>
+  </si>
+  <si>
+    <t>이송엽</t>
+  </si>
+  <si>
+    <t>smfvnfms0615@naver.com</t>
+  </si>
+  <si>
+    <t>국어국문학전공</t>
+  </si>
+  <si>
+    <t>김지나</t>
+  </si>
+  <si>
+    <t>csu1102@naver.com</t>
+  </si>
+  <si>
+    <t>조성운</t>
+  </si>
+  <si>
+    <t>qweryoon0415@gmail.com</t>
+  </si>
+  <si>
+    <t>cheolhyun1234@naver.com</t>
+  </si>
+  <si>
+    <t>박철현</t>
+  </si>
+  <si>
+    <t>llimjh123@naver.com</t>
+  </si>
+  <si>
+    <t>임준완</t>
+  </si>
+  <si>
+    <t>sungjun2558@naver.com</t>
+  </si>
+  <si>
+    <t>박성준</t>
+  </si>
+  <si>
+    <t>seonwoo6034@naver.com</t>
+  </si>
+  <si>
+    <t>이선우</t>
   </si>
 </sst>
 </file>
@@ -2026,7 +2311,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K229" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K273" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -9565,35 +9850,1443 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="20">
+      <c r="A229" s="14">
         <v>45722.88305289352</v>
       </c>
-      <c r="B229" s="21" t="s">
+      <c r="B229" s="15" t="s">
         <v>559</v>
       </c>
-      <c r="C229" s="21" t="s">
+      <c r="C229" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D229" s="21">
+      <c r="D229" s="15">
         <v>2.0191035E7</v>
       </c>
-      <c r="E229" s="21" t="s">
+      <c r="E229" s="15" t="s">
         <v>560</v>
       </c>
-      <c r="F229" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G229" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H229" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I229" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K229" s="22" t="s">
+      <c r="F229" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G229" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H229" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I229" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K229" s="18" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="16">
+        <v>45722.896569432865</v>
+      </c>
+      <c r="B230" s="17" t="s">
+        <v>561</v>
+      </c>
+      <c r="C230" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D230" s="17">
+        <v>2.0192957E7</v>
+      </c>
+      <c r="E230" s="17" t="s">
+        <v>562</v>
+      </c>
+      <c r="F230" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G230" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H230" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I230" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J230" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="14">
+        <v>45722.94919053241</v>
+      </c>
+      <c r="B231" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="C231" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D231" s="15">
+        <v>2.0226628E7</v>
+      </c>
+      <c r="E231" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="F231" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G231" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H231" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I231" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K231" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="16">
+        <v>45723.03477209491</v>
+      </c>
+      <c r="B232" s="17" t="s">
+        <v>565</v>
+      </c>
+      <c r="C232" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D232" s="17">
+        <v>2.0246212E7</v>
+      </c>
+      <c r="E232" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="F232" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G232" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H232" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I232" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K232" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="14">
+        <v>45723.0546368287</v>
+      </c>
+      <c r="B233" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="C233" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D233" s="15">
+        <v>2.0201044E7</v>
+      </c>
+      <c r="E233" s="15" t="s">
+        <v>568</v>
+      </c>
+      <c r="F233" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G233" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H233" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I233" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K233" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="16">
+        <v>45723.26119488426</v>
+      </c>
+      <c r="B234" s="17" t="s">
+        <v>569</v>
+      </c>
+      <c r="C234" s="17" t="s">
+        <v>570</v>
+      </c>
+      <c r="D234" s="17">
+        <v>2.0225188E7</v>
+      </c>
+      <c r="E234" s="17" t="s">
+        <v>571</v>
+      </c>
+      <c r="F234" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G234" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H234" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I234" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K234" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="14">
+        <v>45723.371766296295</v>
+      </c>
+      <c r="B235" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="C235" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D235" s="15">
+        <v>2.0223712E7</v>
+      </c>
+      <c r="E235" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="F235" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G235" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H235" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I235" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K235" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="16">
+        <v>45723.40960130787</v>
+      </c>
+      <c r="B236" s="17" t="s">
+        <v>574</v>
+      </c>
+      <c r="C236" s="17" t="s">
+        <v>575</v>
+      </c>
+      <c r="D236" s="17">
+        <v>2.0243364E7</v>
+      </c>
+      <c r="E236" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="F236" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G236" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H236" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I236" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K236" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="14">
+        <v>45723.49958783565</v>
+      </c>
+      <c r="B237" s="15" t="s">
+        <v>576</v>
+      </c>
+      <c r="C237" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D237" s="15">
+        <v>2.0223002E7</v>
+      </c>
+      <c r="E237" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="F237" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G237" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H237" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I237" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K237" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="16">
+        <v>45723.50487443287</v>
+      </c>
+      <c r="B238" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="C238" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D238" s="17">
+        <v>2.0182936E7</v>
+      </c>
+      <c r="E238" s="17" t="s">
+        <v>579</v>
+      </c>
+      <c r="F238" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G238" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H238" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I238" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J238" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="14">
+        <v>45723.529280682866</v>
+      </c>
+      <c r="B239" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="C239" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D239" s="15">
+        <v>2.0243209E7</v>
+      </c>
+      <c r="E239" s="15" t="s">
+        <v>581</v>
+      </c>
+      <c r="F239" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G239" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H239" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I239" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J239" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="16">
+        <v>45723.55390506945</v>
+      </c>
+      <c r="B240" s="17" t="s">
+        <v>582</v>
+      </c>
+      <c r="C240" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D240" s="17">
+        <v>2.024372E7</v>
+      </c>
+      <c r="E240" s="17" t="s">
+        <v>583</v>
+      </c>
+      <c r="F240" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G240" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H240" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I240" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J240" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="14">
+        <v>45723.59036048611</v>
+      </c>
+      <c r="B241" s="15" t="s">
+        <v>584</v>
+      </c>
+      <c r="C241" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D241" s="15">
+        <v>2.0243532E7</v>
+      </c>
+      <c r="E241" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="F241" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G241" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H241" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I241" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J241" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="16">
+        <v>45723.596658483795</v>
+      </c>
+      <c r="B242" s="17" t="s">
+        <v>586</v>
+      </c>
+      <c r="C242" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D242" s="17">
+        <v>2.0204124E7</v>
+      </c>
+      <c r="E242" s="17" t="s">
+        <v>587</v>
+      </c>
+      <c r="F242" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G242" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H242" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I242" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K242" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="14">
+        <v>45723.61063258102</v>
+      </c>
+      <c r="B243" s="15" t="s">
+        <v>588</v>
+      </c>
+      <c r="C243" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D243" s="15">
+        <v>2.0223716E7</v>
+      </c>
+      <c r="E243" s="15" t="s">
+        <v>589</v>
+      </c>
+      <c r="F243" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G243" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H243" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I243" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J243" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="16">
+        <v>45723.65404883102</v>
+      </c>
+      <c r="B244" s="17" t="s">
+        <v>590</v>
+      </c>
+      <c r="C244" s="17" t="s">
+        <v>591</v>
+      </c>
+      <c r="D244" s="17">
+        <v>2.0215138E7</v>
+      </c>
+      <c r="E244" s="17" t="s">
+        <v>592</v>
+      </c>
+      <c r="F244" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G244" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H244" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I244" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J244" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="14">
+        <v>45723.6575359375</v>
+      </c>
+      <c r="B245" s="15" t="s">
+        <v>593</v>
+      </c>
+      <c r="C245" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D245" s="15">
+        <v>2.0203537E7</v>
+      </c>
+      <c r="E245" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="F245" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G245" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H245" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I245" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J245" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="16">
+        <v>45723.665303368056</v>
+      </c>
+      <c r="B246" s="17" t="s">
+        <v>595</v>
+      </c>
+      <c r="C246" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D246" s="17">
+        <v>2.024621E7</v>
+      </c>
+      <c r="E246" s="17" t="s">
+        <v>596</v>
+      </c>
+      <c r="F246" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G246" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H246" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I246" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K246" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="14">
+        <v>45723.66813114584</v>
+      </c>
+      <c r="B247" s="15" t="s">
+        <v>597</v>
+      </c>
+      <c r="C247" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="D247" s="15">
+        <v>2.0231062E7</v>
+      </c>
+      <c r="E247" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="F247" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G247" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H247" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I247" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J247" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="16">
+        <v>45723.66882662037</v>
+      </c>
+      <c r="B248" s="17" t="s">
+        <v>599</v>
+      </c>
+      <c r="C248" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D248" s="17">
+        <v>2.0202537E7</v>
+      </c>
+      <c r="E248" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="F248" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G248" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H248" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I248" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J248" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="14">
+        <v>45723.67254166667</v>
+      </c>
+      <c r="B249" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="C249" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="D249" s="15">
+        <v>2.0231101E7</v>
+      </c>
+      <c r="E249" s="15" t="s">
+        <v>602</v>
+      </c>
+      <c r="F249" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G249" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H249" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I249" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J249" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="16">
+        <v>45723.687768275464</v>
+      </c>
+      <c r="B250" s="17" t="s">
+        <v>603</v>
+      </c>
+      <c r="C250" s="17" t="s">
+        <v>604</v>
+      </c>
+      <c r="D250" s="17">
+        <v>2.0183242E7</v>
+      </c>
+      <c r="E250" s="17" t="s">
+        <v>605</v>
+      </c>
+      <c r="F250" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G250" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H250" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I250" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K250" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="14">
+        <v>45723.69442451389</v>
+      </c>
+      <c r="B251" s="15" t="s">
+        <v>606</v>
+      </c>
+      <c r="C251" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="D251" s="15">
+        <v>2.0241713E7</v>
+      </c>
+      <c r="E251" s="15" t="s">
+        <v>607</v>
+      </c>
+      <c r="F251" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G251" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H251" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I251" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J251" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="16">
+        <v>45723.69853013889</v>
+      </c>
+      <c r="B252" s="17" t="s">
+        <v>608</v>
+      </c>
+      <c r="C252" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="D252" s="17">
+        <v>2.0243229E7</v>
+      </c>
+      <c r="E252" s="17" t="s">
+        <v>609</v>
+      </c>
+      <c r="F252" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G252" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H252" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I252" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J252" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="14">
+        <v>45723.69889888889</v>
+      </c>
+      <c r="B253" s="15" t="s">
+        <v>610</v>
+      </c>
+      <c r="C253" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D253" s="15">
+        <v>2.0242849E7</v>
+      </c>
+      <c r="E253" s="15" t="s">
+        <v>611</v>
+      </c>
+      <c r="F253" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G253" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H253" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I253" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K253" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="16">
+        <v>45723.703406099536</v>
+      </c>
+      <c r="B254" s="17" t="s">
+        <v>612</v>
+      </c>
+      <c r="C254" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D254" s="17">
+        <v>2.021707E7</v>
+      </c>
+      <c r="E254" s="17" t="s">
+        <v>613</v>
+      </c>
+      <c r="F254" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G254" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H254" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I254" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J254" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="14">
+        <v>45723.703836712964</v>
+      </c>
+      <c r="B255" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="C255" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D255" s="15">
+        <v>2.0246211E7</v>
+      </c>
+      <c r="E255" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="F255" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G255" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H255" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I255" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K255" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="16">
+        <v>45723.756482592595</v>
+      </c>
+      <c r="B256" s="17" t="s">
+        <v>616</v>
+      </c>
+      <c r="C256" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D256" s="17">
+        <v>2.0232613E7</v>
+      </c>
+      <c r="E256" s="17" t="s">
+        <v>617</v>
+      </c>
+      <c r="F256" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G256" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H256" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I256" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J256" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="14">
+        <v>45723.78285158565</v>
+      </c>
+      <c r="B257" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="C257" s="15" t="s">
+        <v>619</v>
+      </c>
+      <c r="D257" s="15">
+        <v>2.024106E7</v>
+      </c>
+      <c r="E257" s="15" t="s">
+        <v>620</v>
+      </c>
+      <c r="F257" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G257" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H257" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I257" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J257" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="16">
+        <v>45723.78523840278</v>
+      </c>
+      <c r="B258" s="17" t="s">
+        <v>621</v>
+      </c>
+      <c r="C258" s="17" t="s">
+        <v>622</v>
+      </c>
+      <c r="D258" s="17">
+        <v>2.0251066E7</v>
+      </c>
+      <c r="E258" s="17" t="s">
+        <v>622</v>
+      </c>
+      <c r="F258" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G258" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H258" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I258" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J258" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="14">
+        <v>45723.79318766204</v>
+      </c>
+      <c r="B259" s="15" t="s">
+        <v>623</v>
+      </c>
+      <c r="C259" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="D259" s="15">
+        <v>2.0256637E7</v>
+      </c>
+      <c r="E259" s="15" t="s">
+        <v>624</v>
+      </c>
+      <c r="F259" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G259" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H259" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I259" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K259" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="16">
+        <v>45723.80107585648</v>
+      </c>
+      <c r="B260" s="17" t="s">
+        <v>625</v>
+      </c>
+      <c r="C260" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D260" s="17">
+        <v>2.0243012E7</v>
+      </c>
+      <c r="E260" s="17" t="s">
+        <v>626</v>
+      </c>
+      <c r="F260" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G260" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H260" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="I260" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K260" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="14">
+        <v>45723.82332809028</v>
+      </c>
+      <c r="B261" s="15" t="s">
+        <v>627</v>
+      </c>
+      <c r="C261" s="15" t="s">
+        <v>628</v>
+      </c>
+      <c r="D261" s="15">
+        <v>2.0243252E7</v>
+      </c>
+      <c r="E261" s="15" t="s">
+        <v>629</v>
+      </c>
+      <c r="F261" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G261" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H261" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I261" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K261" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="16">
+        <v>45723.90133258102</v>
+      </c>
+      <c r="B262" s="17" t="s">
+        <v>630</v>
+      </c>
+      <c r="C262" s="17" t="s">
+        <v>631</v>
+      </c>
+      <c r="D262" s="17">
+        <v>2.022326E7</v>
+      </c>
+      <c r="E262" s="17" t="s">
+        <v>632</v>
+      </c>
+      <c r="F262" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G262" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H262" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I262" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K262" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="14">
+        <v>45723.90895650463</v>
+      </c>
+      <c r="B263" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="C263" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="D263" s="15">
+        <v>2.0242322E7</v>
+      </c>
+      <c r="E263" s="15" t="s">
+        <v>634</v>
+      </c>
+      <c r="F263" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G263" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H263" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I263" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K263" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="16">
+        <v>45723.915255949076</v>
+      </c>
+      <c r="B264" s="17" t="s">
+        <v>635</v>
+      </c>
+      <c r="C264" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D264" s="17">
+        <v>2.024271E7</v>
+      </c>
+      <c r="E264" s="17" t="s">
+        <v>636</v>
+      </c>
+      <c r="F264" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G264" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H264" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I264" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J264" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="14">
+        <v>45723.933469131945</v>
+      </c>
+      <c r="B265" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="C265" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D265" s="15">
+        <v>2.0212976E7</v>
+      </c>
+      <c r="E265" s="15" t="s">
+        <v>638</v>
+      </c>
+      <c r="F265" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G265" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H265" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I265" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J265" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="16">
+        <v>45723.93953346065</v>
+      </c>
+      <c r="B266" s="17" t="s">
+        <v>639</v>
+      </c>
+      <c r="C266" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="D266" s="17">
+        <v>2.0242999E7</v>
+      </c>
+      <c r="E266" s="17" t="s">
+        <v>641</v>
+      </c>
+      <c r="F266" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G266" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H266" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I266" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J266" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="14">
+        <v>45723.939730474536</v>
+      </c>
+      <c r="B267" s="15" t="s">
+        <v>642</v>
+      </c>
+      <c r="C267" s="15" t="s">
+        <v>643</v>
+      </c>
+      <c r="D267" s="15">
+        <v>2.0221021E7</v>
+      </c>
+      <c r="E267" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="F267" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G267" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H267" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I267" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K267" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="16">
+        <v>45723.946173634264</v>
+      </c>
+      <c r="B268" s="17" t="s">
+        <v>645</v>
+      </c>
+      <c r="C268" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D268" s="17">
+        <v>2.0223044E7</v>
+      </c>
+      <c r="E268" s="17" t="s">
+        <v>646</v>
+      </c>
+      <c r="F268" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G268" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H268" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I268" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J268" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="14">
+        <v>45723.955245115736</v>
+      </c>
+      <c r="B269" s="15" t="s">
+        <v>647</v>
+      </c>
+      <c r="C269" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D269" s="15">
+        <v>2.0245212E7</v>
+      </c>
+      <c r="E269" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="F269" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G269" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H269" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I269" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K269" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="16">
+        <v>45724.031485590276</v>
+      </c>
+      <c r="B270" s="17" t="s">
+        <v>648</v>
+      </c>
+      <c r="C270" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D270" s="17">
+        <v>2.024272E7</v>
+      </c>
+      <c r="E270" s="17" t="s">
+        <v>649</v>
+      </c>
+      <c r="F270" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G270" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H270" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I270" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K270" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="14">
+        <v>45724.03470846065</v>
+      </c>
+      <c r="B271" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="C271" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D271" s="15">
+        <v>2.0225239E7</v>
+      </c>
+      <c r="E271" s="15" t="s">
+        <v>651</v>
+      </c>
+      <c r="F271" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G271" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H271" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I271" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J271" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="16">
+        <v>45724.140149768515</v>
+      </c>
+      <c r="B272" s="17" t="s">
+        <v>652</v>
+      </c>
+      <c r="C272" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="D272" s="17">
+        <v>2.021332E7</v>
+      </c>
+      <c r="E272" s="17" t="s">
+        <v>653</v>
+      </c>
+      <c r="F272" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G272" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H272" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I272" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J272" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="20">
+        <v>45724.14028497685</v>
+      </c>
+      <c r="B273" s="21" t="s">
+        <v>654</v>
+      </c>
+      <c r="C273" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D273" s="21">
+        <v>2.0244133E7</v>
+      </c>
+      <c r="E273" s="21" t="s">
+        <v>655</v>
+      </c>
+      <c r="F273" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G273" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H273" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I273" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K273" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250303.xlsx
+++ b/R/data/quiz_250303.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3091" uniqueCount="887">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -1979,6 +1979,699 @@
   </si>
   <si>
     <t>이선우</t>
+  </si>
+  <si>
+    <t>guswjd052428@naver.com</t>
+  </si>
+  <si>
+    <t>전현정</t>
+  </si>
+  <si>
+    <t>ko095013@naver.com</t>
+  </si>
+  <si>
+    <t>고준영</t>
+  </si>
+  <si>
+    <t>a1b20802@gmail.com</t>
+  </si>
+  <si>
+    <t>이도연</t>
+  </si>
+  <si>
+    <t>zesprie@naver.com</t>
+  </si>
+  <si>
+    <t>강미소</t>
+  </si>
+  <si>
+    <t>ysj030412@gmail.com</t>
+  </si>
+  <si>
+    <t>윤성중</t>
+  </si>
+  <si>
+    <t>eunha12314@naver.com</t>
+  </si>
+  <si>
+    <t>경규남</t>
+  </si>
+  <si>
+    <t>0205ysm@naver.com</t>
+  </si>
+  <si>
+    <t>유승민</t>
+  </si>
+  <si>
+    <t>dltldms0908@naver.com</t>
+  </si>
+  <si>
+    <t>이시은</t>
+  </si>
+  <si>
+    <t>nkav1234@naver.com</t>
+  </si>
+  <si>
+    <t>박종민</t>
+  </si>
+  <si>
+    <t>jaenn103@naver.com</t>
+  </si>
+  <si>
+    <t>김재원</t>
+  </si>
+  <si>
+    <t>ehclfjqm@naver.com</t>
+  </si>
+  <si>
+    <t>변수현</t>
+  </si>
+  <si>
+    <t>monkey5301@naver.com</t>
+  </si>
+  <si>
+    <t>최원형</t>
+  </si>
+  <si>
+    <t>jung5jung59708@gmail.com</t>
+  </si>
+  <si>
+    <t>정서현</t>
+  </si>
+  <si>
+    <t>hyunjinfc2015@gmail.com</t>
+  </si>
+  <si>
+    <t>김현진</t>
+  </si>
+  <si>
+    <t>yookh114@gmail.com</t>
+  </si>
+  <si>
+    <t>유강현</t>
+  </si>
+  <si>
+    <t>kiss040924@gmail.com</t>
+  </si>
+  <si>
+    <t>김무원</t>
+  </si>
+  <si>
+    <t>wookyung7536@naver.com</t>
+  </si>
+  <si>
+    <t>양우경</t>
+  </si>
+  <si>
+    <t>junsung872@gmail.com</t>
+  </si>
+  <si>
+    <t>윤준성</t>
+  </si>
+  <si>
+    <t>vskadudv@nate.com</t>
+  </si>
+  <si>
+    <t>김남영</t>
+  </si>
+  <si>
+    <t>hby9364@naver.com</t>
+  </si>
+  <si>
+    <t>황보연</t>
+  </si>
+  <si>
+    <t>seoyeonjang0418@naver.com</t>
+  </si>
+  <si>
+    <t>장서연</t>
+  </si>
+  <si>
+    <t>hrk5353@naver.com</t>
+  </si>
+  <si>
+    <t>홍리경</t>
+  </si>
+  <si>
+    <t>linaeun2004@naver.com</t>
+  </si>
+  <si>
+    <t>nick6723@naver.com</t>
+  </si>
+  <si>
+    <t>미래융합스쿨 의약신소재공학과</t>
+  </si>
+  <si>
+    <t>유준상</t>
+  </si>
+  <si>
+    <t>dbsrhkdid5@naver.com</t>
+  </si>
+  <si>
+    <t>박태양</t>
+  </si>
+  <si>
+    <t>kses12058@gmail.com</t>
+  </si>
+  <si>
+    <t>김도현</t>
+  </si>
+  <si>
+    <t>idhyunmook@gmail.com</t>
+  </si>
+  <si>
+    <t>강현묵</t>
+  </si>
+  <si>
+    <t>yelin0612@naver.com</t>
+  </si>
+  <si>
+    <t>권예린</t>
+  </si>
+  <si>
+    <t>lminseok1228@gmail.com</t>
+  </si>
+  <si>
+    <t>이민석</t>
+  </si>
+  <si>
+    <t>jk385272@gmail.com</t>
+  </si>
+  <si>
+    <t>kimgg0324@naver.com</t>
+  </si>
+  <si>
+    <t>김기건</t>
+  </si>
+  <si>
+    <t>ggt0826@naver.com</t>
+  </si>
+  <si>
+    <t>김경태</t>
+  </si>
+  <si>
+    <t>kdh000224@naver.com</t>
+  </si>
+  <si>
+    <t>김동현</t>
+  </si>
+  <si>
+    <t>kass3210@naver.com</t>
+  </si>
+  <si>
+    <t>박대광</t>
+  </si>
+  <si>
+    <t>jun050510@naver.com</t>
+  </si>
+  <si>
+    <t>유한준</t>
+  </si>
+  <si>
+    <t>alexju0519@gmail.com</t>
+  </si>
+  <si>
+    <t>주호연</t>
+  </si>
+  <si>
+    <t>yourim1207@naver.com</t>
+  </si>
+  <si>
+    <t>오유림</t>
+  </si>
+  <si>
+    <t>rga0801@naver.com</t>
+  </si>
+  <si>
+    <t>김형민</t>
+  </si>
+  <si>
+    <t>hoe978034@gmail.com</t>
+  </si>
+  <si>
+    <t>이호은</t>
+  </si>
+  <si>
+    <t>tmddms0604@maver.com</t>
+  </si>
+  <si>
+    <t>김승은</t>
+  </si>
+  <si>
+    <t>tj5854566@naver.com</t>
+  </si>
+  <si>
+    <t>박서희</t>
+  </si>
+  <si>
+    <t>gyuha8489@gmail.com</t>
+  </si>
+  <si>
+    <t>김유하</t>
+  </si>
+  <si>
+    <t>jmk104904@naver.com</t>
+  </si>
+  <si>
+    <t>정민기</t>
+  </si>
+  <si>
+    <t>kwan0172@gmail.com</t>
+  </si>
+  <si>
+    <t>김관형</t>
+  </si>
+  <si>
+    <t>chayoung1205@gmail.com</t>
+  </si>
+  <si>
+    <t>김찬영</t>
+  </si>
+  <si>
+    <t>hb3130@naver.com</t>
+  </si>
+  <si>
+    <t>안효빈</t>
+  </si>
+  <si>
+    <t>parkjuheok0420@gmail.com</t>
+  </si>
+  <si>
+    <t>박주혁</t>
+  </si>
+  <si>
+    <t>dlwngud77777@naver.com</t>
+  </si>
+  <si>
+    <t>이주형</t>
+  </si>
+  <si>
+    <t>lsa3173@naver.com</t>
+  </si>
+  <si>
+    <t>임승언</t>
+  </si>
+  <si>
+    <t>kelly9845@naver.com</t>
+  </si>
+  <si>
+    <t>박서연</t>
+  </si>
+  <si>
+    <t>haroldchoi0504@gmail.com</t>
+  </si>
+  <si>
+    <t>소프트웨어학과</t>
+  </si>
+  <si>
+    <t>최현준</t>
+  </si>
+  <si>
+    <t>wshs_ws@naver.com</t>
+  </si>
+  <si>
+    <t>컨텐츠IT</t>
+  </si>
+  <si>
+    <t>이우성</t>
+  </si>
+  <si>
+    <t>a01033294075@gmail.com</t>
+  </si>
+  <si>
+    <t>임혜원</t>
+  </si>
+  <si>
+    <t>hanmaim89@gmail.com</t>
+  </si>
+  <si>
+    <t>wjdtjdbs8926@naver.com</t>
+  </si>
+  <si>
+    <t>정서윤</t>
+  </si>
+  <si>
+    <t>yun0501255@naver.com</t>
+  </si>
+  <si>
+    <t>윤어진</t>
+  </si>
+  <si>
+    <t>lym051211-@naver.com</t>
+  </si>
+  <si>
+    <t>이예빈</t>
+  </si>
+  <si>
+    <t>seokzard10@naver.com</t>
+  </si>
+  <si>
+    <t>진현석</t>
+  </si>
+  <si>
+    <t>hyuk7515@naver.com</t>
+  </si>
+  <si>
+    <t>김동혁</t>
+  </si>
+  <si>
+    <t>0103020410@daum.net</t>
+  </si>
+  <si>
+    <t>김준형</t>
+  </si>
+  <si>
+    <t>lgn0915@naver.com</t>
+  </si>
+  <si>
+    <t>임지인</t>
+  </si>
+  <si>
+    <t>a.to.the.z.1087@gmail.com</t>
+  </si>
+  <si>
+    <t>김지혜</t>
+  </si>
+  <si>
+    <t>yeon2760@naver.com</t>
+  </si>
+  <si>
+    <t>강나연</t>
+  </si>
+  <si>
+    <t>justin99961@gmail.com</t>
+  </si>
+  <si>
+    <t>조연서</t>
+  </si>
+  <si>
+    <t>qkrwogus030103@naver.com</t>
+  </si>
+  <si>
+    <t>인문학부</t>
+  </si>
+  <si>
+    <t>박재현</t>
+  </si>
+  <si>
+    <t>20233006@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>shin19980527@gmail.com</t>
+  </si>
+  <si>
+    <t>신재헌</t>
+  </si>
+  <si>
+    <t>song_050929@naver.com</t>
+  </si>
+  <si>
+    <t>송은채</t>
+  </si>
+  <si>
+    <t>deoduck877@naver.com</t>
+  </si>
+  <si>
+    <t>김동규</t>
+  </si>
+  <si>
+    <t>eunseo041320@naver.com</t>
+  </si>
+  <si>
+    <t>이은서</t>
+  </si>
+  <si>
+    <t>won00814@naver.com</t>
+  </si>
+  <si>
+    <t>이혜원</t>
+  </si>
+  <si>
+    <t>20236637@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>디지털인문예술</t>
+  </si>
+  <si>
+    <t>최나연</t>
+  </si>
+  <si>
+    <t>ksw0226611@naver.com</t>
+  </si>
+  <si>
+    <t>김성욱</t>
+  </si>
+  <si>
+    <t>yooyoungjune@naver.com</t>
+  </si>
+  <si>
+    <t>유영준</t>
+  </si>
+  <si>
+    <t>ksyprosch11@gmail.com</t>
+  </si>
+  <si>
+    <t>김서연</t>
+  </si>
+  <si>
+    <t>kim9301204@gmail.com</t>
+  </si>
+  <si>
+    <t>소대현</t>
+  </si>
+  <si>
+    <t>twins.sijin@gmail.com</t>
+  </si>
+  <si>
+    <t>정시진</t>
+  </si>
+  <si>
+    <t>mikyoung327586@gmail.com</t>
+  </si>
+  <si>
+    <t>박찬희</t>
+  </si>
+  <si>
+    <t>xhsh030408@naver.com</t>
+  </si>
+  <si>
+    <t>황성현</t>
+  </si>
+  <si>
+    <t>binkim112@gmail.com</t>
+  </si>
+  <si>
+    <t>김종빈</t>
+  </si>
+  <si>
+    <t>2005jkjk@naver.com</t>
+  </si>
+  <si>
+    <t>최나윤</t>
+  </si>
+  <si>
+    <t>hull7614@gmail.com</t>
+  </si>
+  <si>
+    <t>남궁효경</t>
+  </si>
+  <si>
+    <t>jackkhc02@naver.com</t>
+  </si>
+  <si>
+    <t>철학</t>
+  </si>
+  <si>
+    <t>김세윤</t>
+  </si>
+  <si>
+    <t>difeded@naver.com</t>
+  </si>
+  <si>
+    <t>박혜인</t>
+  </si>
+  <si>
+    <t>minjj0918@naver.com</t>
+  </si>
+  <si>
+    <t>조석훈</t>
+  </si>
+  <si>
+    <t>younsu0625@naver.com</t>
+  </si>
+  <si>
+    <t>임윤수</t>
+  </si>
+  <si>
+    <t>hongu038@gmail.com</t>
+  </si>
+  <si>
+    <t>홍우진</t>
+  </si>
+  <si>
+    <t>tkdgnl0206@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">법학과 </t>
+  </si>
+  <si>
+    <t>이상휘</t>
+  </si>
+  <si>
+    <t>geuna7411@gmail.com</t>
+  </si>
+  <si>
+    <t>박근아</t>
+  </si>
+  <si>
+    <t>skdda1073@naver.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인공지능융합학부 </t>
+  </si>
+  <si>
+    <t>고경완</t>
+  </si>
+  <si>
+    <t>jwseok0218@naver.com</t>
+  </si>
+  <si>
+    <t>조우석</t>
+  </si>
+  <si>
+    <t>hyunkyung1410@naver.com</t>
+  </si>
+  <si>
+    <t>최현경</t>
+  </si>
+  <si>
+    <t>echanwoo48@naver.com</t>
+  </si>
+  <si>
+    <t>이찬우</t>
+  </si>
+  <si>
+    <t>llyj0202@gmail.com</t>
+  </si>
+  <si>
+    <t>이유정</t>
+  </si>
+  <si>
+    <t>2013bin@naver.com</t>
+  </si>
+  <si>
+    <t>박유빈</t>
+  </si>
+  <si>
+    <t>wjdgksdla@naver.com</t>
+  </si>
+  <si>
+    <t>이정한</t>
+  </si>
+  <si>
+    <t>rang26781@naver.com</t>
+  </si>
+  <si>
+    <t>신서원</t>
+  </si>
+  <si>
+    <t>taekwonlmj@gmail.com</t>
+  </si>
+  <si>
+    <t>이미주</t>
+  </si>
+  <si>
+    <t>namsoy0405@naver.com</t>
+  </si>
+  <si>
+    <t>남소영</t>
+  </si>
+  <si>
+    <t>work777ys@gmail.com</t>
+  </si>
+  <si>
+    <t>정선영</t>
+  </si>
+  <si>
+    <t>ncc07291@naver.com</t>
+  </si>
+  <si>
+    <t>신기재</t>
+  </si>
+  <si>
+    <t>woojoong0221@gmail.com</t>
+  </si>
+  <si>
+    <t>김우중</t>
+  </si>
+  <si>
+    <t>adtobcan1@naver.com</t>
+  </si>
+  <si>
+    <t>서재영</t>
+  </si>
+  <si>
+    <t>gagahyun335@naver.com</t>
+  </si>
+  <si>
+    <t>이가현</t>
+  </si>
+  <si>
+    <t>dytpq0823@naver.com</t>
+  </si>
+  <si>
+    <t>이한울</t>
+  </si>
+  <si>
+    <t>nody0402@naver.com</t>
+  </si>
+  <si>
+    <t>소프트웨어융합대학 빅데이터 전공</t>
+  </si>
+  <si>
+    <t>박준우</t>
+  </si>
+  <si>
+    <t>autumngo77@gmail.com</t>
+  </si>
+  <si>
+    <t>미래융합스쿨 융합신소재</t>
+  </si>
+  <si>
+    <t>고나영</t>
+  </si>
+  <si>
+    <t>jsy40394725@gmail.com</t>
+  </si>
+  <si>
+    <t>조선영</t>
+  </si>
+  <si>
+    <t>minser9265@gmail.com</t>
+  </si>
+  <si>
+    <t>cksdudaa@gmail.com</t>
+  </si>
+  <si>
+    <t>정찬영</t>
+  </si>
+  <si>
+    <t>20242640@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>황가현</t>
+  </si>
+  <si>
+    <t>lhp050705@gmail.com</t>
+  </si>
+  <si>
+    <t>이현표</t>
+  </si>
+  <si>
+    <t>h20221222@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>박현우</t>
   </si>
 </sst>
 </file>
@@ -2009,7 +2702,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -2142,10 +2835,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -2153,27 +2846,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -2183,7 +2862,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2250,9 +2929,6 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2311,7 +2987,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K273" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K386" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -11258,35 +11934,3651 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="20">
+      <c r="A273" s="14">
         <v>45724.14028497685</v>
       </c>
-      <c r="B273" s="21" t="s">
+      <c r="B273" s="15" t="s">
         <v>654</v>
       </c>
-      <c r="C273" s="21" t="s">
+      <c r="C273" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D273" s="21">
+      <c r="D273" s="15">
         <v>2.0244133E7</v>
       </c>
-      <c r="E273" s="21" t="s">
+      <c r="E273" s="15" t="s">
         <v>655</v>
       </c>
-      <c r="F273" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G273" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H273" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I273" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K273" s="22" t="s">
+      <c r="F273" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G273" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H273" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I273" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K273" s="18" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="16">
+        <v>45724.40531886574</v>
+      </c>
+      <c r="B274" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="C274" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D274" s="17">
+        <v>2.0243029E7</v>
+      </c>
+      <c r="E274" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="F274" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G274" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H274" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I274" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K274" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="14">
+        <v>45724.46422288194</v>
+      </c>
+      <c r="B275" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="C275" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D275" s="15">
+        <v>2.0212403E7</v>
+      </c>
+      <c r="E275" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="F275" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G275" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H275" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I275" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K275" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="16">
+        <v>45724.4795771875</v>
+      </c>
+      <c r="B276" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="C276" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="D276" s="17">
+        <v>2.0245216E7</v>
+      </c>
+      <c r="E276" s="17" t="s">
+        <v>661</v>
+      </c>
+      <c r="F276" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G276" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H276" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I276" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J276" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="14">
+        <v>45724.493308136574</v>
+      </c>
+      <c r="B277" s="15" t="s">
+        <v>662</v>
+      </c>
+      <c r="C277" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D277" s="15">
+        <v>2.0182101E7</v>
+      </c>
+      <c r="E277" s="15" t="s">
+        <v>663</v>
+      </c>
+      <c r="F277" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G277" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H277" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I277" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J277" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="16">
+        <v>45724.50968478009</v>
+      </c>
+      <c r="B278" s="17" t="s">
+        <v>664</v>
+      </c>
+      <c r="C278" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="D278" s="17">
+        <v>2.0223331E7</v>
+      </c>
+      <c r="E278" s="17" t="s">
+        <v>665</v>
+      </c>
+      <c r="F278" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G278" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H278" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I278" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K278" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="14">
+        <v>45724.50977415509</v>
+      </c>
+      <c r="B279" s="15" t="s">
+        <v>666</v>
+      </c>
+      <c r="C279" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="D279" s="15">
+        <v>2.0223302E7</v>
+      </c>
+      <c r="E279" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="F279" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G279" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H279" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I279" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K279" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="16">
+        <v>45724.50978716435</v>
+      </c>
+      <c r="B280" s="17" t="s">
+        <v>668</v>
+      </c>
+      <c r="C280" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="D280" s="17">
+        <v>2.0223329E7</v>
+      </c>
+      <c r="E280" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="F280" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G280" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H280" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I280" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J280" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="14">
+        <v>45724.54216182871</v>
+      </c>
+      <c r="B281" s="15" t="s">
+        <v>670</v>
+      </c>
+      <c r="C281" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="D281" s="15">
+        <v>2.0231068E7</v>
+      </c>
+      <c r="E281" s="15" t="s">
+        <v>671</v>
+      </c>
+      <c r="F281" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G281" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H281" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I281" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K281" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="16">
+        <v>45724.543034745366</v>
+      </c>
+      <c r="B282" s="17" t="s">
+        <v>672</v>
+      </c>
+      <c r="C282" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D282" s="17">
+        <v>2.0224116E7</v>
+      </c>
+      <c r="E282" s="17" t="s">
+        <v>673</v>
+      </c>
+      <c r="F282" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G282" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H282" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I282" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J282" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="14">
+        <v>45724.55665398148</v>
+      </c>
+      <c r="B283" s="15" t="s">
+        <v>674</v>
+      </c>
+      <c r="C283" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D283" s="15">
+        <v>2.0236228E7</v>
+      </c>
+      <c r="E283" s="15" t="s">
+        <v>675</v>
+      </c>
+      <c r="F283" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G283" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H283" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I283" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K283" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="16">
+        <v>45724.60147591435</v>
+      </c>
+      <c r="B284" s="17" t="s">
+        <v>676</v>
+      </c>
+      <c r="C284" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D284" s="17">
+        <v>2.0223821E7</v>
+      </c>
+      <c r="E284" s="17" t="s">
+        <v>677</v>
+      </c>
+      <c r="F284" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G284" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H284" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I284" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J284" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="14">
+        <v>45724.61003935186</v>
+      </c>
+      <c r="B285" s="15" t="s">
+        <v>678</v>
+      </c>
+      <c r="C285" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D285" s="15">
+        <v>2.0203735E7</v>
+      </c>
+      <c r="E285" s="15" t="s">
+        <v>679</v>
+      </c>
+      <c r="F285" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G285" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H285" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I285" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K285" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="16">
+        <v>45724.62220329861</v>
+      </c>
+      <c r="B286" s="17" t="s">
+        <v>680</v>
+      </c>
+      <c r="C286" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D286" s="17">
+        <v>2.0242744E7</v>
+      </c>
+      <c r="E286" s="17" t="s">
+        <v>681</v>
+      </c>
+      <c r="F286" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G286" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H286" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I286" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K286" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="14">
+        <v>45724.63822569445</v>
+      </c>
+      <c r="B287" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="C287" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="D287" s="15">
+        <v>2.0241028E7</v>
+      </c>
+      <c r="E287" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="F287" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G287" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H287" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I287" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J287" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="16">
+        <v>45724.66279326389</v>
+      </c>
+      <c r="B288" s="17" t="s">
+        <v>684</v>
+      </c>
+      <c r="C288" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="D288" s="17">
+        <v>2.0245209E7</v>
+      </c>
+      <c r="E288" s="17" t="s">
+        <v>685</v>
+      </c>
+      <c r="F288" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G288" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H288" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I288" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J288" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="14">
+        <v>45724.679204201384</v>
+      </c>
+      <c r="B289" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="C289" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D289" s="15">
+        <v>2.023101E7</v>
+      </c>
+      <c r="E289" s="15" t="s">
+        <v>687</v>
+      </c>
+      <c r="F289" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G289" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H289" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I289" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J289" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="16">
+        <v>45724.69247876157</v>
+      </c>
+      <c r="B290" s="17" t="s">
+        <v>688</v>
+      </c>
+      <c r="C290" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D290" s="17">
+        <v>2.0212223E7</v>
+      </c>
+      <c r="E290" s="17" t="s">
+        <v>689</v>
+      </c>
+      <c r="F290" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G290" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H290" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I290" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J290" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="14">
+        <v>45724.69262408565</v>
+      </c>
+      <c r="B291" s="15" t="s">
+        <v>690</v>
+      </c>
+      <c r="C291" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D291" s="15">
+        <v>2.024393E7</v>
+      </c>
+      <c r="E291" s="15" t="s">
+        <v>691</v>
+      </c>
+      <c r="F291" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G291" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H291" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I291" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K291" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="16">
+        <v>45724.70400215278</v>
+      </c>
+      <c r="B292" s="17" t="s">
+        <v>692</v>
+      </c>
+      <c r="C292" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="D292" s="17">
+        <v>2.0227145E7</v>
+      </c>
+      <c r="E292" s="17" t="s">
+        <v>693</v>
+      </c>
+      <c r="F292" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G292" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H292" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I292" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K292" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="14">
+        <v>45724.73466579861</v>
+      </c>
+      <c r="B293" s="15" t="s">
+        <v>694</v>
+      </c>
+      <c r="C293" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D293" s="15">
+        <v>2.0254146E7</v>
+      </c>
+      <c r="E293" s="15" t="s">
+        <v>695</v>
+      </c>
+      <c r="F293" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G293" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H293" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I293" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K293" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="16">
+        <v>45724.741755104165</v>
+      </c>
+      <c r="B294" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="C294" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D294" s="17">
+        <v>2.0241232E7</v>
+      </c>
+      <c r="E294" s="17" t="s">
+        <v>697</v>
+      </c>
+      <c r="F294" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G294" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H294" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I294" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J294" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="14">
+        <v>45724.74583193287</v>
+      </c>
+      <c r="B295" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="C295" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D295" s="15">
+        <v>2.0242588E7</v>
+      </c>
+      <c r="E295" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="F295" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G295" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H295" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I295" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J295" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="16">
+        <v>45724.75112997685</v>
+      </c>
+      <c r="B296" s="17" t="s">
+        <v>700</v>
+      </c>
+      <c r="C296" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D296" s="17">
+        <v>2.0246272E7</v>
+      </c>
+      <c r="E296" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="F296" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G296" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H296" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I296" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J296" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="14">
+        <v>45724.77124155093</v>
+      </c>
+      <c r="B297" s="15" t="s">
+        <v>701</v>
+      </c>
+      <c r="C297" s="15" t="s">
+        <v>702</v>
+      </c>
+      <c r="D297" s="15">
+        <v>2.0216626E7</v>
+      </c>
+      <c r="E297" s="15" t="s">
+        <v>703</v>
+      </c>
+      <c r="F297" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G297" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H297" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I297" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K297" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="16">
+        <v>45724.79714472222</v>
+      </c>
+      <c r="B298" s="17" t="s">
+        <v>704</v>
+      </c>
+      <c r="C298" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="D298" s="17">
+        <v>2.0195174E7</v>
+      </c>
+      <c r="E298" s="17" t="s">
+        <v>705</v>
+      </c>
+      <c r="F298" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G298" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H298" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I298" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K298" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="14">
+        <v>45724.83230599537</v>
+      </c>
+      <c r="B299" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="C299" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D299" s="15">
+        <v>2.024292E7</v>
+      </c>
+      <c r="E299" s="15" t="s">
+        <v>707</v>
+      </c>
+      <c r="F299" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G299" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H299" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I299" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K299" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="16">
+        <v>45724.841499525464</v>
+      </c>
+      <c r="B300" s="17" t="s">
+        <v>708</v>
+      </c>
+      <c r="C300" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D300" s="17">
+        <v>2.0214102E7</v>
+      </c>
+      <c r="E300" s="17" t="s">
+        <v>709</v>
+      </c>
+      <c r="F300" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G300" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H300" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I300" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K300" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="14">
+        <v>45724.852566319445</v>
+      </c>
+      <c r="B301" s="15" t="s">
+        <v>710</v>
+      </c>
+      <c r="C301" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D301" s="15">
+        <v>2.0213905E7</v>
+      </c>
+      <c r="E301" s="15" t="s">
+        <v>711</v>
+      </c>
+      <c r="F301" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G301" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H301" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I301" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J301" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="16">
+        <v>45724.866182962964</v>
+      </c>
+      <c r="B302" s="17" t="s">
+        <v>712</v>
+      </c>
+      <c r="C302" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D302" s="17">
+        <v>2.0245219E7</v>
+      </c>
+      <c r="E302" s="17" t="s">
+        <v>713</v>
+      </c>
+      <c r="F302" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G302" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H302" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I302" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K302" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="14">
+        <v>45724.891575127316</v>
+      </c>
+      <c r="B303" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="C303" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D303" s="15">
+        <v>2.0243614E7</v>
+      </c>
+      <c r="E303" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="F303" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G303" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H303" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I303" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J303" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="16">
+        <v>45724.89843126158</v>
+      </c>
+      <c r="B304" s="17" t="s">
+        <v>715</v>
+      </c>
+      <c r="C304" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D304" s="17">
+        <v>2.0242917E7</v>
+      </c>
+      <c r="E304" s="17" t="s">
+        <v>716</v>
+      </c>
+      <c r="F304" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G304" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H304" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I304" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J304" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="14">
+        <v>45724.919040787034</v>
+      </c>
+      <c r="B305" s="15" t="s">
+        <v>717</v>
+      </c>
+      <c r="C305" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D305" s="15">
+        <v>2.0212703E7</v>
+      </c>
+      <c r="E305" s="15" t="s">
+        <v>718</v>
+      </c>
+      <c r="F305" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G305" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H305" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I305" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J305" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="16">
+        <v>45724.948106041666</v>
+      </c>
+      <c r="B306" s="17" t="s">
+        <v>719</v>
+      </c>
+      <c r="C306" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D306" s="17">
+        <v>2.0202913E7</v>
+      </c>
+      <c r="E306" s="17" t="s">
+        <v>720</v>
+      </c>
+      <c r="F306" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G306" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H306" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I306" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J306" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="14">
+        <v>45724.949831157406</v>
+      </c>
+      <c r="B307" s="15" t="s">
+        <v>721</v>
+      </c>
+      <c r="C307" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D307" s="15">
+        <v>2.0212721E7</v>
+      </c>
+      <c r="E307" s="15" t="s">
+        <v>722</v>
+      </c>
+      <c r="F307" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G307" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H307" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I307" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J307" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="16">
+        <v>45724.966032118056</v>
+      </c>
+      <c r="B308" s="17" t="s">
+        <v>723</v>
+      </c>
+      <c r="C308" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="D308" s="17">
+        <v>2.0241528E7</v>
+      </c>
+      <c r="E308" s="17" t="s">
+        <v>724</v>
+      </c>
+      <c r="F308" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G308" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H308" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I308" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J308" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="14">
+        <v>45724.97083362269</v>
+      </c>
+      <c r="B309" s="15" t="s">
+        <v>725</v>
+      </c>
+      <c r="C309" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D309" s="15">
+        <v>2.0243039E7</v>
+      </c>
+      <c r="E309" s="15" t="s">
+        <v>726</v>
+      </c>
+      <c r="F309" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G309" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H309" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I309" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K309" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="16">
+        <v>45724.982434652775</v>
+      </c>
+      <c r="B310" s="17" t="s">
+        <v>727</v>
+      </c>
+      <c r="C310" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D310" s="17">
+        <v>2.0242223E7</v>
+      </c>
+      <c r="E310" s="17" t="s">
+        <v>728</v>
+      </c>
+      <c r="F310" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G310" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H310" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I310" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K310" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="14">
+        <v>45724.983309131945</v>
+      </c>
+      <c r="B311" s="15" t="s">
+        <v>729</v>
+      </c>
+      <c r="C311" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D311" s="15">
+        <v>2.0215146E7</v>
+      </c>
+      <c r="E311" s="15" t="s">
+        <v>730</v>
+      </c>
+      <c r="F311" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G311" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H311" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I311" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K311" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="16">
+        <v>45724.992368136576</v>
+      </c>
+      <c r="B312" s="17" t="s">
+        <v>731</v>
+      </c>
+      <c r="C312" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D312" s="17">
+        <v>2.0243837E7</v>
+      </c>
+      <c r="E312" s="17" t="s">
+        <v>732</v>
+      </c>
+      <c r="F312" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G312" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H312" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I312" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K312" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="14">
+        <v>45724.992983819444</v>
+      </c>
+      <c r="B313" s="15" t="s">
+        <v>733</v>
+      </c>
+      <c r="C313" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D313" s="15">
+        <v>2.0241607E7</v>
+      </c>
+      <c r="E313" s="15" t="s">
+        <v>734</v>
+      </c>
+      <c r="F313" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G313" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H313" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I313" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J313" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="16">
+        <v>45724.99765972223</v>
+      </c>
+      <c r="B314" s="17" t="s">
+        <v>735</v>
+      </c>
+      <c r="C314" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D314" s="17">
+        <v>2.0222116E7</v>
+      </c>
+      <c r="E314" s="17" t="s">
+        <v>736</v>
+      </c>
+      <c r="F314" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G314" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H314" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I314" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J314" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="14">
+        <v>45725.019365914355</v>
+      </c>
+      <c r="B315" s="15" t="s">
+        <v>737</v>
+      </c>
+      <c r="C315" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D315" s="15">
+        <v>2.024102E7</v>
+      </c>
+      <c r="E315" s="15" t="s">
+        <v>738</v>
+      </c>
+      <c r="F315" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G315" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H315" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I315" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J315" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="16">
+        <v>45725.05499546297</v>
+      </c>
+      <c r="B316" s="17" t="s">
+        <v>739</v>
+      </c>
+      <c r="C316" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D316" s="17">
+        <v>2.0244144E7</v>
+      </c>
+      <c r="E316" s="17" t="s">
+        <v>740</v>
+      </c>
+      <c r="F316" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G316" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H316" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="I316" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J316" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="14">
+        <v>45725.05871627315</v>
+      </c>
+      <c r="B317" s="15" t="s">
+        <v>741</v>
+      </c>
+      <c r="C317" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D317" s="15">
+        <v>2.021291E7</v>
+      </c>
+      <c r="E317" s="15" t="s">
+        <v>742</v>
+      </c>
+      <c r="F317" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G317" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H317" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I317" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J317" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="16">
+        <v>45725.097162743055</v>
+      </c>
+      <c r="B318" s="17" t="s">
+        <v>743</v>
+      </c>
+      <c r="C318" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D318" s="17">
+        <v>2.0223512E7</v>
+      </c>
+      <c r="E318" s="17" t="s">
+        <v>744</v>
+      </c>
+      <c r="F318" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G318" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H318" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I318" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J318" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="14">
+        <v>45725.10297502315</v>
+      </c>
+      <c r="B319" s="15" t="s">
+        <v>745</v>
+      </c>
+      <c r="C319" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D319" s="15">
+        <v>2.0241216E7</v>
+      </c>
+      <c r="E319" s="15" t="s">
+        <v>746</v>
+      </c>
+      <c r="F319" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G319" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H319" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I319" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J319" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="16">
+        <v>45725.158235173614</v>
+      </c>
+      <c r="B320" s="17" t="s">
+        <v>747</v>
+      </c>
+      <c r="C320" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D320" s="17">
+        <v>2.0223517E7</v>
+      </c>
+      <c r="E320" s="17" t="s">
+        <v>748</v>
+      </c>
+      <c r="F320" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G320" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H320" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I320" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K320" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="14">
+        <v>45725.23300011574</v>
+      </c>
+      <c r="B321" s="15" t="s">
+        <v>749</v>
+      </c>
+      <c r="C321" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D321" s="15">
+        <v>2.0194143E7</v>
+      </c>
+      <c r="E321" s="15" t="s">
+        <v>750</v>
+      </c>
+      <c r="F321" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G321" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H321" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I321" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K321" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="16">
+        <v>45725.37000098379</v>
+      </c>
+      <c r="B322" s="17" t="s">
+        <v>751</v>
+      </c>
+      <c r="C322" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D322" s="17">
+        <v>2.0226281E7</v>
+      </c>
+      <c r="E322" s="17" t="s">
+        <v>752</v>
+      </c>
+      <c r="F322" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G322" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H322" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I322" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J322" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="14">
+        <v>45725.3898981713</v>
+      </c>
+      <c r="B323" s="15" t="s">
+        <v>753</v>
+      </c>
+      <c r="C323" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D323" s="15">
+        <v>2.0223515E7</v>
+      </c>
+      <c r="E323" s="15" t="s">
+        <v>754</v>
+      </c>
+      <c r="F323" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G323" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H323" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I323" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J323" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="16">
+        <v>45725.39135181713</v>
+      </c>
+      <c r="B324" s="17" t="s">
+        <v>755</v>
+      </c>
+      <c r="C324" s="17" t="s">
+        <v>756</v>
+      </c>
+      <c r="D324" s="17">
+        <v>2.0255271E7</v>
+      </c>
+      <c r="E324" s="17" t="s">
+        <v>757</v>
+      </c>
+      <c r="F324" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G324" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H324" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I324" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K324" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="14">
+        <v>45725.40766545139</v>
+      </c>
+      <c r="B325" s="15" t="s">
+        <v>758</v>
+      </c>
+      <c r="C325" s="15" t="s">
+        <v>759</v>
+      </c>
+      <c r="D325" s="15">
+        <v>2.0237104E7</v>
+      </c>
+      <c r="E325" s="15" t="s">
+        <v>760</v>
+      </c>
+      <c r="F325" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G325" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H325" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I325" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J325" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="16">
+        <v>45725.42466684028</v>
+      </c>
+      <c r="B326" s="17" t="s">
+        <v>761</v>
+      </c>
+      <c r="C326" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D326" s="17">
+        <v>2.0243023E7</v>
+      </c>
+      <c r="E326" s="17" t="s">
+        <v>762</v>
+      </c>
+      <c r="F326" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G326" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H326" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I326" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K326" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="14">
+        <v>45725.43403605324</v>
+      </c>
+      <c r="B327" s="15" t="s">
+        <v>763</v>
+      </c>
+      <c r="C327" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D327" s="15">
+        <v>2.0253006E7</v>
+      </c>
+      <c r="E327" s="15" t="s">
+        <v>671</v>
+      </c>
+      <c r="F327" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G327" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H327" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I327" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J327" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="16">
+        <v>45725.45825606481</v>
+      </c>
+      <c r="B328" s="17" t="s">
+        <v>764</v>
+      </c>
+      <c r="C328" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D328" s="17">
+        <v>2.024109E7</v>
+      </c>
+      <c r="E328" s="17" t="s">
+        <v>765</v>
+      </c>
+      <c r="F328" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G328" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H328" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I328" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J328" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="14">
+        <v>45725.47662767361</v>
+      </c>
+      <c r="B329" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="C329" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D329" s="15">
+        <v>2.0243831E7</v>
+      </c>
+      <c r="E329" s="15" t="s">
+        <v>767</v>
+      </c>
+      <c r="F329" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G329" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H329" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I329" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J329" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="16">
+        <v>45725.48361393518</v>
+      </c>
+      <c r="B330" s="17" t="s">
+        <v>768</v>
+      </c>
+      <c r="C330" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D330" s="17">
+        <v>2.0243633E7</v>
+      </c>
+      <c r="E330" s="17" t="s">
+        <v>769</v>
+      </c>
+      <c r="F330" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G330" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H330" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I330" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K330" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="14">
+        <v>45725.49444446759</v>
+      </c>
+      <c r="B331" s="15" t="s">
+        <v>770</v>
+      </c>
+      <c r="C331" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D331" s="15">
+        <v>2.0246424E7</v>
+      </c>
+      <c r="E331" s="15" t="s">
+        <v>771</v>
+      </c>
+      <c r="F331" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G331" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H331" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I331" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J331" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="16">
+        <v>45725.4967233912</v>
+      </c>
+      <c r="B332" s="17" t="s">
+        <v>772</v>
+      </c>
+      <c r="C332" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D332" s="17">
+        <v>2.0224103E7</v>
+      </c>
+      <c r="E332" s="17" t="s">
+        <v>773</v>
+      </c>
+      <c r="F332" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G332" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H332" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I332" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K332" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="14">
+        <v>45725.50555375</v>
+      </c>
+      <c r="B333" s="15" t="s">
+        <v>774</v>
+      </c>
+      <c r="C333" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="D333" s="15">
+        <v>2.0215136E7</v>
+      </c>
+      <c r="E333" s="15" t="s">
+        <v>775</v>
+      </c>
+      <c r="F333" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G333" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H333" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I333" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J333" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="16">
+        <v>45725.53979560186</v>
+      </c>
+      <c r="B334" s="17" t="s">
+        <v>776</v>
+      </c>
+      <c r="C334" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D334" s="17">
+        <v>2.0243944E7</v>
+      </c>
+      <c r="E334" s="17" t="s">
+        <v>777</v>
+      </c>
+      <c r="F334" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G334" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H334" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I334" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K334" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="14">
+        <v>45725.54115803241</v>
+      </c>
+      <c r="B335" s="15" t="s">
+        <v>778</v>
+      </c>
+      <c r="C335" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D335" s="15">
+        <v>2.0242713E7</v>
+      </c>
+      <c r="E335" s="15" t="s">
+        <v>779</v>
+      </c>
+      <c r="F335" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G335" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H335" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I335" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K335" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="16">
+        <v>45725.55342221065</v>
+      </c>
+      <c r="B336" s="17" t="s">
+        <v>780</v>
+      </c>
+      <c r="C336" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D336" s="17">
+        <v>2.0233901E7</v>
+      </c>
+      <c r="E336" s="17" t="s">
+        <v>781</v>
+      </c>
+      <c r="F336" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G336" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H336" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I336" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J336" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="14">
+        <v>45725.569372314814</v>
+      </c>
+      <c r="B337" s="15" t="s">
+        <v>782</v>
+      </c>
+      <c r="C337" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D337" s="15">
+        <v>2.0196285E7</v>
+      </c>
+      <c r="E337" s="15" t="s">
+        <v>783</v>
+      </c>
+      <c r="F337" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G337" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H337" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I337" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J337" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="16">
+        <v>45725.58285494213</v>
+      </c>
+      <c r="B338" s="17" t="s">
+        <v>784</v>
+      </c>
+      <c r="C338" s="17" t="s">
+        <v>785</v>
+      </c>
+      <c r="D338" s="17">
+        <v>2.0231039E7</v>
+      </c>
+      <c r="E338" s="17" t="s">
+        <v>786</v>
+      </c>
+      <c r="F338" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G338" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H338" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I338" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K338" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="14">
+        <v>45725.62002328703</v>
+      </c>
+      <c r="B339" s="15" t="s">
+        <v>787</v>
+      </c>
+      <c r="C339" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D339" s="15">
+        <v>2.0233006E7</v>
+      </c>
+      <c r="E339" s="15" t="s">
+        <v>655</v>
+      </c>
+      <c r="F339" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G339" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H339" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I339" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K339" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="16">
+        <v>45725.62655940972</v>
+      </c>
+      <c r="B340" s="17" t="s">
+        <v>788</v>
+      </c>
+      <c r="C340" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D340" s="17">
+        <v>2.0171054E7</v>
+      </c>
+      <c r="E340" s="17" t="s">
+        <v>789</v>
+      </c>
+      <c r="F340" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G340" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H340" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I340" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K340" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="14">
+        <v>45725.63126504629</v>
+      </c>
+      <c r="B341" s="15" t="s">
+        <v>790</v>
+      </c>
+      <c r="C341" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D341" s="15">
+        <v>2.0241049E7</v>
+      </c>
+      <c r="E341" s="15" t="s">
+        <v>791</v>
+      </c>
+      <c r="F341" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G341" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H341" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I341" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K341" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="16">
+        <v>45725.63864793981</v>
+      </c>
+      <c r="B342" s="17" t="s">
+        <v>792</v>
+      </c>
+      <c r="C342" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D342" s="17">
+        <v>2.0195122E7</v>
+      </c>
+      <c r="E342" s="17" t="s">
+        <v>793</v>
+      </c>
+      <c r="F342" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G342" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H342" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I342" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J342" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="14">
+        <v>45725.64141831019</v>
+      </c>
+      <c r="B343" s="15" t="s">
+        <v>794</v>
+      </c>
+      <c r="C343" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D343" s="15">
+        <v>2.0243009E7</v>
+      </c>
+      <c r="E343" s="15" t="s">
+        <v>795</v>
+      </c>
+      <c r="F343" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G343" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H343" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I343" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K343" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="16">
+        <v>45725.64358741898</v>
+      </c>
+      <c r="B344" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="C344" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="D344" s="17">
+        <v>2.0242345E7</v>
+      </c>
+      <c r="E344" s="17" t="s">
+        <v>797</v>
+      </c>
+      <c r="F344" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G344" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H344" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I344" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J344" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="14">
+        <v>45725.646825821765</v>
+      </c>
+      <c r="B345" s="15" t="s">
+        <v>798</v>
+      </c>
+      <c r="C345" s="15" t="s">
+        <v>799</v>
+      </c>
+      <c r="D345" s="15">
+        <v>2.0236637E7</v>
+      </c>
+      <c r="E345" s="15" t="s">
+        <v>800</v>
+      </c>
+      <c r="F345" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G345" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H345" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I345" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J345" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="16">
+        <v>45725.653102013894</v>
+      </c>
+      <c r="B346" s="17" t="s">
+        <v>801</v>
+      </c>
+      <c r="C346" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="D346" s="17">
+        <v>2.0241704E7</v>
+      </c>
+      <c r="E346" s="17" t="s">
+        <v>802</v>
+      </c>
+      <c r="F346" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G346" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H346" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I346" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J346" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="14">
+        <v>45725.655608368055</v>
+      </c>
+      <c r="B347" s="15" t="s">
+        <v>803</v>
+      </c>
+      <c r="C347" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="D347" s="15">
+        <v>2.0216739E7</v>
+      </c>
+      <c r="E347" s="15" t="s">
+        <v>804</v>
+      </c>
+      <c r="F347" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G347" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H347" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I347" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J347" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="16">
+        <v>45725.662036064816</v>
+      </c>
+      <c r="B348" s="17" t="s">
+        <v>805</v>
+      </c>
+      <c r="C348" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D348" s="17">
+        <v>2.0245129E7</v>
+      </c>
+      <c r="E348" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="F348" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G348" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H348" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I348" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K348" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="14">
+        <v>45725.66435184028</v>
+      </c>
+      <c r="B349" s="15" t="s">
+        <v>807</v>
+      </c>
+      <c r="C349" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D349" s="15">
+        <v>2.0193716E7</v>
+      </c>
+      <c r="E349" s="15" t="s">
+        <v>808</v>
+      </c>
+      <c r="F349" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G349" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H349" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I349" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J349" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="16">
+        <v>45725.67912439815</v>
+      </c>
+      <c r="B350" s="17" t="s">
+        <v>809</v>
+      </c>
+      <c r="C350" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="D350" s="17">
+        <v>2.0221534E7</v>
+      </c>
+      <c r="E350" s="17" t="s">
+        <v>810</v>
+      </c>
+      <c r="F350" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G350" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H350" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I350" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J350" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="14">
+        <v>45725.68048068287</v>
+      </c>
+      <c r="B351" s="15" t="s">
+        <v>811</v>
+      </c>
+      <c r="C351" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D351" s="15">
+        <v>2.0242523E7</v>
+      </c>
+      <c r="E351" s="15" t="s">
+        <v>812</v>
+      </c>
+      <c r="F351" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G351" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H351" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I351" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K351" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="16">
+        <v>45725.701550011574</v>
+      </c>
+      <c r="B352" s="17" t="s">
+        <v>813</v>
+      </c>
+      <c r="C352" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D352" s="17">
+        <v>2.0223063E7</v>
+      </c>
+      <c r="E352" s="17" t="s">
+        <v>814</v>
+      </c>
+      <c r="F352" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G352" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H352" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I352" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J352" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="14">
+        <v>45725.709793981485</v>
+      </c>
+      <c r="B353" s="15" t="s">
+        <v>815</v>
+      </c>
+      <c r="C353" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D353" s="15">
+        <v>2.024211E7</v>
+      </c>
+      <c r="E353" s="15" t="s">
+        <v>816</v>
+      </c>
+      <c r="F353" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G353" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H353" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I353" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J353" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="16">
+        <v>45725.71066736111</v>
+      </c>
+      <c r="B354" s="17" t="s">
+        <v>817</v>
+      </c>
+      <c r="C354" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D354" s="17">
+        <v>2.0246426E7</v>
+      </c>
+      <c r="E354" s="17" t="s">
+        <v>818</v>
+      </c>
+      <c r="F354" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G354" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H354" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I354" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J354" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="14">
+        <v>45725.72931296296</v>
+      </c>
+      <c r="B355" s="15" t="s">
+        <v>819</v>
+      </c>
+      <c r="C355" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D355" s="15">
+        <v>2.0242218E7</v>
+      </c>
+      <c r="E355" s="15" t="s">
+        <v>820</v>
+      </c>
+      <c r="F355" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G355" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H355" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I355" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J355" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="16">
+        <v>45725.73980833333</v>
+      </c>
+      <c r="B356" s="17" t="s">
+        <v>821</v>
+      </c>
+      <c r="C356" s="17" t="s">
+        <v>822</v>
+      </c>
+      <c r="D356" s="17">
+        <v>2.0211021E7</v>
+      </c>
+      <c r="E356" s="17" t="s">
+        <v>823</v>
+      </c>
+      <c r="F356" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G356" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H356" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I356" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J356" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="14">
+        <v>45725.74399310185</v>
+      </c>
+      <c r="B357" s="15" t="s">
+        <v>824</v>
+      </c>
+      <c r="C357" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D357" s="15">
+        <v>2.0242967E7</v>
+      </c>
+      <c r="E357" s="15" t="s">
+        <v>825</v>
+      </c>
+      <c r="F357" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G357" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H357" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I357" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J357" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="16">
+        <v>45725.74620460648</v>
+      </c>
+      <c r="B358" s="17" t="s">
+        <v>826</v>
+      </c>
+      <c r="C358" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="D358" s="17">
+        <v>2.0246777E7</v>
+      </c>
+      <c r="E358" s="17" t="s">
+        <v>827</v>
+      </c>
+      <c r="F358" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G358" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H358" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I358" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J358" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="14">
+        <v>45725.75027908565</v>
+      </c>
+      <c r="B359" s="15" t="s">
+        <v>828</v>
+      </c>
+      <c r="C359" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D359" s="15">
+        <v>2.0224139E7</v>
+      </c>
+      <c r="E359" s="15" t="s">
+        <v>829</v>
+      </c>
+      <c r="F359" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G359" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H359" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I359" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K359" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="16">
+        <v>45725.75153554398</v>
+      </c>
+      <c r="B360" s="17" t="s">
+        <v>830</v>
+      </c>
+      <c r="C360" s="17" t="s">
+        <v>604</v>
+      </c>
+      <c r="D360" s="17">
+        <v>2.0193262E7</v>
+      </c>
+      <c r="E360" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="F360" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G360" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H360" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I360" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K360" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="14">
+        <v>45725.75252025463</v>
+      </c>
+      <c r="B361" s="15" t="s">
+        <v>832</v>
+      </c>
+      <c r="C361" s="15" t="s">
+        <v>833</v>
+      </c>
+      <c r="D361" s="15">
+        <v>2.0192742E7</v>
+      </c>
+      <c r="E361" s="15" t="s">
+        <v>834</v>
+      </c>
+      <c r="F361" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G361" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H361" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I361" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J361" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="16">
+        <v>45725.753561261576</v>
+      </c>
+      <c r="B362" s="17" t="s">
+        <v>835</v>
+      </c>
+      <c r="C362" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D362" s="17">
+        <v>2.024351E7</v>
+      </c>
+      <c r="E362" s="17" t="s">
+        <v>836</v>
+      </c>
+      <c r="F362" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G362" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H362" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I362" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K362" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="14">
+        <v>45725.77122221065</v>
+      </c>
+      <c r="B363" s="15" t="s">
+        <v>837</v>
+      </c>
+      <c r="C363" s="15" t="s">
+        <v>838</v>
+      </c>
+      <c r="D363" s="15">
+        <v>2.0226702E7</v>
+      </c>
+      <c r="E363" s="15" t="s">
+        <v>839</v>
+      </c>
+      <c r="F363" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G363" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H363" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I363" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J363" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="16">
+        <v>45725.77881309028</v>
+      </c>
+      <c r="B364" s="17" t="s">
+        <v>840</v>
+      </c>
+      <c r="C364" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="D364" s="17">
+        <v>2.0201731E7</v>
+      </c>
+      <c r="E364" s="17" t="s">
+        <v>841</v>
+      </c>
+      <c r="F364" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G364" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H364" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I364" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K364" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="14">
+        <v>45725.784285381946</v>
+      </c>
+      <c r="B365" s="15" t="s">
+        <v>842</v>
+      </c>
+      <c r="C365" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="D365" s="15">
+        <v>2.0242583E7</v>
+      </c>
+      <c r="E365" s="15" t="s">
+        <v>843</v>
+      </c>
+      <c r="F365" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G365" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H365" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I365" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J365" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="16">
+        <v>45725.79411232639</v>
+      </c>
+      <c r="B366" s="17" t="s">
+        <v>844</v>
+      </c>
+      <c r="C366" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D366" s="17">
+        <v>2.0224134E7</v>
+      </c>
+      <c r="E366" s="17" t="s">
+        <v>845</v>
+      </c>
+      <c r="F366" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G366" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H366" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I366" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J366" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="14">
+        <v>45725.79554665509</v>
+      </c>
+      <c r="B367" s="15" t="s">
+        <v>846</v>
+      </c>
+      <c r="C367" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D367" s="15">
+        <v>2.0227071E7</v>
+      </c>
+      <c r="E367" s="15" t="s">
+        <v>847</v>
+      </c>
+      <c r="F367" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G367" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H367" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I367" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K367" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="16">
+        <v>45725.799839467596</v>
+      </c>
+      <c r="B368" s="17" t="s">
+        <v>848</v>
+      </c>
+      <c r="C368" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D368" s="17">
+        <v>2.020412E7</v>
+      </c>
+      <c r="E368" s="17" t="s">
+        <v>849</v>
+      </c>
+      <c r="F368" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G368" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H368" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I368" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K368" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="14">
+        <v>45725.800226990745</v>
+      </c>
+      <c r="B369" s="15" t="s">
+        <v>850</v>
+      </c>
+      <c r="C369" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="D369" s="15">
+        <v>2.0203021E7</v>
+      </c>
+      <c r="E369" s="15" t="s">
+        <v>851</v>
+      </c>
+      <c r="F369" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G369" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H369" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I369" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K369" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="16">
+        <v>45725.812615324074</v>
+      </c>
+      <c r="B370" s="17" t="s">
+        <v>852</v>
+      </c>
+      <c r="C370" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D370" s="17">
+        <v>2.024162E7</v>
+      </c>
+      <c r="E370" s="17" t="s">
+        <v>853</v>
+      </c>
+      <c r="F370" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G370" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H370" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I370" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K370" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="14">
+        <v>45725.81439616898</v>
+      </c>
+      <c r="B371" s="15" t="s">
+        <v>854</v>
+      </c>
+      <c r="C371" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D371" s="15">
+        <v>2.0253236E7</v>
+      </c>
+      <c r="E371" s="15" t="s">
+        <v>855</v>
+      </c>
+      <c r="F371" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G371" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H371" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I371" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J371" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="16">
+        <v>45725.81704622685</v>
+      </c>
+      <c r="B372" s="17" t="s">
+        <v>856</v>
+      </c>
+      <c r="C372" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D372" s="17">
+        <v>2.0226409E7</v>
+      </c>
+      <c r="E372" s="17" t="s">
+        <v>857</v>
+      </c>
+      <c r="F372" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G372" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H372" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I372" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J372" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="14">
+        <v>45725.81756549768</v>
+      </c>
+      <c r="B373" s="15" t="s">
+        <v>858</v>
+      </c>
+      <c r="C373" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D373" s="15">
+        <v>2.0223428E7</v>
+      </c>
+      <c r="E373" s="15" t="s">
+        <v>859</v>
+      </c>
+      <c r="F373" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G373" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H373" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I373" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K373" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="16">
+        <v>45725.82050081019</v>
+      </c>
+      <c r="B374" s="17" t="s">
+        <v>860</v>
+      </c>
+      <c r="C374" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D374" s="17">
+        <v>2.0192216E7</v>
+      </c>
+      <c r="E374" s="17" t="s">
+        <v>861</v>
+      </c>
+      <c r="F374" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G374" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H374" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I374" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K374" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="14">
+        <v>45725.821663587965</v>
+      </c>
+      <c r="B375" s="15" t="s">
+        <v>862</v>
+      </c>
+      <c r="C375" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="D375" s="15">
+        <v>2.0246617E7</v>
+      </c>
+      <c r="E375" s="15" t="s">
+        <v>863</v>
+      </c>
+      <c r="F375" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G375" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H375" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I375" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K375" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="16">
+        <v>45725.853799965276</v>
+      </c>
+      <c r="B376" s="17" t="s">
+        <v>864</v>
+      </c>
+      <c r="C376" s="17" t="s">
+        <v>604</v>
+      </c>
+      <c r="D376" s="17">
+        <v>2.0243226E7</v>
+      </c>
+      <c r="E376" s="17" t="s">
+        <v>865</v>
+      </c>
+      <c r="F376" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G376" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H376" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I376" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J376" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="14">
+        <v>45725.85584123843</v>
+      </c>
+      <c r="B377" s="15" t="s">
+        <v>866</v>
+      </c>
+      <c r="C377" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="D377" s="15">
+        <v>2.0212997E7</v>
+      </c>
+      <c r="E377" s="15" t="s">
+        <v>867</v>
+      </c>
+      <c r="F377" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G377" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H377" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I377" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K377" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="16">
+        <v>45725.863755185186</v>
+      </c>
+      <c r="B378" s="17" t="s">
+        <v>868</v>
+      </c>
+      <c r="C378" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D378" s="17">
+        <v>2.0253018E7</v>
+      </c>
+      <c r="E378" s="17" t="s">
+        <v>869</v>
+      </c>
+      <c r="F378" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G378" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H378" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I378" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J378" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="14">
+        <v>45725.869348622684</v>
+      </c>
+      <c r="B379" s="15" t="s">
+        <v>870</v>
+      </c>
+      <c r="C379" s="15" t="s">
+        <v>871</v>
+      </c>
+      <c r="D379" s="15">
+        <v>2.0225163E7</v>
+      </c>
+      <c r="E379" s="15" t="s">
+        <v>872</v>
+      </c>
+      <c r="F379" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G379" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H379" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I379" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K379" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="16">
+        <v>45725.878039351854</v>
+      </c>
+      <c r="B380" s="17" t="s">
+        <v>873</v>
+      </c>
+      <c r="C380" s="17" t="s">
+        <v>874</v>
+      </c>
+      <c r="D380" s="17">
+        <v>2.0246605E7</v>
+      </c>
+      <c r="E380" s="17" t="s">
+        <v>875</v>
+      </c>
+      <c r="F380" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G380" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H380" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I380" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K380" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="14">
+        <v>45725.87895827546</v>
+      </c>
+      <c r="B381" s="15" t="s">
+        <v>876</v>
+      </c>
+      <c r="C381" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D381" s="15">
+        <v>2.0222634E7</v>
+      </c>
+      <c r="E381" s="15" t="s">
+        <v>877</v>
+      </c>
+      <c r="F381" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G381" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H381" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I381" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J381" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="16">
+        <v>45725.87965570602</v>
+      </c>
+      <c r="B382" s="17" t="s">
+        <v>878</v>
+      </c>
+      <c r="C382" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D382" s="17">
+        <v>2.0252433E7</v>
+      </c>
+      <c r="E382" s="17" t="s">
+        <v>624</v>
+      </c>
+      <c r="F382" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G382" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H382" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I382" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J382" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="14">
+        <v>45725.888956759256</v>
+      </c>
+      <c r="B383" s="15" t="s">
+        <v>879</v>
+      </c>
+      <c r="C383" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D383" s="15">
+        <v>2.0213039E7</v>
+      </c>
+      <c r="E383" s="15" t="s">
+        <v>880</v>
+      </c>
+      <c r="F383" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G383" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H383" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I383" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J383" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="16">
+        <v>45725.89740645833</v>
+      </c>
+      <c r="B384" s="17" t="s">
+        <v>881</v>
+      </c>
+      <c r="C384" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D384" s="17">
+        <v>2.024264E7</v>
+      </c>
+      <c r="E384" s="17" t="s">
+        <v>882</v>
+      </c>
+      <c r="F384" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G384" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H384" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I384" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K384" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="14">
+        <v>45725.898034224534</v>
+      </c>
+      <c r="B385" s="15" t="s">
+        <v>883</v>
+      </c>
+      <c r="C385" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D385" s="15">
+        <v>2.0243942E7</v>
+      </c>
+      <c r="E385" s="15" t="s">
+        <v>884</v>
+      </c>
+      <c r="F385" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G385" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H385" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I385" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J385" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="20">
+        <v>45725.89917803241</v>
+      </c>
+      <c r="B386" s="21" t="s">
+        <v>885</v>
+      </c>
+      <c r="C386" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D386" s="21">
+        <v>2.0221222E7</v>
+      </c>
+      <c r="E386" s="21" t="s">
+        <v>886</v>
+      </c>
+      <c r="F386" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G386" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H386" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I386" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J386" s="21" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250303.xlsx
+++ b/R/data/quiz_250303.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3091" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3251" uniqueCount="929">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2672,6 +2672,132 @@
   </si>
   <si>
     <t>박현우</t>
+  </si>
+  <si>
+    <t>rlawhdgus1212@gmail.com</t>
+  </si>
+  <si>
+    <t>김종현</t>
+  </si>
+  <si>
+    <t>min88278610@gmail.com</t>
+  </si>
+  <si>
+    <t>민선주</t>
+  </si>
+  <si>
+    <t>llrkhn11@naver.com</t>
+  </si>
+  <si>
+    <t>임가현</t>
+  </si>
+  <si>
+    <t>h20241226@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>이주연</t>
+  </si>
+  <si>
+    <t>renatta@naver.com</t>
+  </si>
+  <si>
+    <t>이예원</t>
+  </si>
+  <si>
+    <t>junhalee4079@naver.com</t>
+  </si>
+  <si>
+    <t>이준하</t>
+  </si>
+  <si>
+    <t>hclee2891@naver.com</t>
+  </si>
+  <si>
+    <t>이학찬</t>
+  </si>
+  <si>
+    <t>kimjw030112@naver.com</t>
+  </si>
+  <si>
+    <t>김종우</t>
+  </si>
+  <si>
+    <t>pyo9630@gmail.com</t>
+  </si>
+  <si>
+    <t>이충영</t>
+  </si>
+  <si>
+    <t>yourmylife00@naver.com</t>
+  </si>
+  <si>
+    <t>허윤진</t>
+  </si>
+  <si>
+    <t>gka4057@naver.com</t>
+  </si>
+  <si>
+    <t>함효린</t>
+  </si>
+  <si>
+    <t>bshtt2927@gmail.com</t>
+  </si>
+  <si>
+    <t>변세현</t>
+  </si>
+  <si>
+    <t>dami1232@naver.com</t>
+  </si>
+  <si>
+    <t>김경재</t>
+  </si>
+  <si>
+    <t>qga0303@naver.com</t>
+  </si>
+  <si>
+    <t>박하민</t>
+  </si>
+  <si>
+    <t>english3849@naver.com</t>
+  </si>
+  <si>
+    <t>장서린</t>
+  </si>
+  <si>
+    <t>sswskb71538@naver.com</t>
+  </si>
+  <si>
+    <t>신승우</t>
+  </si>
+  <si>
+    <t>her0507050@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">생명과학과 </t>
+  </si>
+  <si>
+    <t>유지훈</t>
+  </si>
+  <si>
+    <t>dlwldn010108@naver.com</t>
+  </si>
+  <si>
+    <t>이지우</t>
+  </si>
+  <si>
+    <t>jahee0114@gmail.com</t>
+  </si>
+  <si>
+    <t>최재희</t>
+  </si>
+  <si>
+    <t>ychoe119@gmail.com</t>
+  </si>
+  <si>
+    <t>글로벌비즈니스전공</t>
+  </si>
+  <si>
+    <t>최윤서</t>
   </si>
 </sst>
 </file>
@@ -2702,7 +2828,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border/>
     <border>
       <left style="thin">
@@ -2858,11 +2984,25 @@
         <color rgb="FF442F65"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2929,6 +3069,9 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2987,7 +3130,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K386" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K406" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -15550,35 +15693,675 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="20">
+      <c r="A386" s="16">
         <v>45725.89917803241</v>
       </c>
-      <c r="B386" s="21" t="s">
+      <c r="B386" s="17" t="s">
         <v>885</v>
       </c>
-      <c r="C386" s="21" t="s">
+      <c r="C386" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D386" s="21">
+      <c r="D386" s="17">
         <v>2.0221222E7</v>
       </c>
-      <c r="E386" s="21" t="s">
+      <c r="E386" s="17" t="s">
         <v>886</v>
       </c>
-      <c r="F386" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G386" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H386" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I386" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="J386" s="21" t="s">
+      <c r="F386" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G386" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H386" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I386" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J386" s="17" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="14">
+        <v>45725.94423577546</v>
+      </c>
+      <c r="B387" s="15" t="s">
+        <v>887</v>
+      </c>
+      <c r="C387" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D387" s="15">
+        <v>2.0192844E7</v>
+      </c>
+      <c r="E387" s="15" t="s">
+        <v>888</v>
+      </c>
+      <c r="F387" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G387" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H387" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I387" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K387" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="16">
+        <v>45725.94658984954</v>
+      </c>
+      <c r="B388" s="17" t="s">
+        <v>889</v>
+      </c>
+      <c r="C388" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D388" s="17">
+        <v>2.0242616E7</v>
+      </c>
+      <c r="E388" s="17" t="s">
+        <v>890</v>
+      </c>
+      <c r="F388" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G388" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H388" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I388" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K388" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="14">
+        <v>45725.951287488424</v>
+      </c>
+      <c r="B389" s="15" t="s">
+        <v>891</v>
+      </c>
+      <c r="C389" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D389" s="15">
+        <v>2.0243943E7</v>
+      </c>
+      <c r="E389" s="15" t="s">
+        <v>892</v>
+      </c>
+      <c r="F389" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G389" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H389" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I389" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K389" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="16">
+        <v>45725.968586250005</v>
+      </c>
+      <c r="B390" s="17" t="s">
+        <v>893</v>
+      </c>
+      <c r="C390" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D390" s="17">
+        <v>2.0241226E7</v>
+      </c>
+      <c r="E390" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="F390" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G390" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H390" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I390" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K390" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="14">
+        <v>45725.97468101852</v>
+      </c>
+      <c r="B391" s="15" t="s">
+        <v>895</v>
+      </c>
+      <c r="C391" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="D391" s="15">
+        <v>2.0242337E7</v>
+      </c>
+      <c r="E391" s="15" t="s">
+        <v>896</v>
+      </c>
+      <c r="F391" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G391" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H391" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I391" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K391" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="16">
+        <v>45726.004724432874</v>
+      </c>
+      <c r="B392" s="17" t="s">
+        <v>897</v>
+      </c>
+      <c r="C392" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D392" s="17">
+        <v>2.0214135E7</v>
+      </c>
+      <c r="E392" s="17" t="s">
+        <v>898</v>
+      </c>
+      <c r="F392" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G392" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H392" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I392" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K392" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="14">
+        <v>45726.347792615736</v>
+      </c>
+      <c r="B393" s="15" t="s">
+        <v>899</v>
+      </c>
+      <c r="C393" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D393" s="15">
+        <v>2.0223529E7</v>
+      </c>
+      <c r="E393" s="15" t="s">
+        <v>900</v>
+      </c>
+      <c r="F393" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G393" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H393" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I393" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J393" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="16">
+        <v>45726.43643366898</v>
+      </c>
+      <c r="B394" s="17" t="s">
+        <v>901</v>
+      </c>
+      <c r="C394" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D394" s="17">
+        <v>2.022411E7</v>
+      </c>
+      <c r="E394" s="17" t="s">
+        <v>902</v>
+      </c>
+      <c r="F394" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G394" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H394" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I394" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J394" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="14">
+        <v>45726.455455324074</v>
+      </c>
+      <c r="B395" s="15" t="s">
+        <v>903</v>
+      </c>
+      <c r="C395" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D395" s="15">
+        <v>2.0222427E7</v>
+      </c>
+      <c r="E395" s="15" t="s">
+        <v>904</v>
+      </c>
+      <c r="F395" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G395" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H395" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I395" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K395" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="16">
+        <v>45726.53576645833</v>
+      </c>
+      <c r="B396" s="17" t="s">
+        <v>905</v>
+      </c>
+      <c r="C396" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D396" s="17">
+        <v>2.0221111E7</v>
+      </c>
+      <c r="E396" s="17" t="s">
+        <v>906</v>
+      </c>
+      <c r="F396" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G396" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H396" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I396" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K396" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="14">
+        <v>45726.57575304398</v>
+      </c>
+      <c r="B397" s="15" t="s">
+        <v>907</v>
+      </c>
+      <c r="C397" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D397" s="15">
+        <v>2.0243848E7</v>
+      </c>
+      <c r="E397" s="15" t="s">
+        <v>908</v>
+      </c>
+      <c r="F397" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G397" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H397" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I397" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K397" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="16">
+        <v>45726.57630699074</v>
+      </c>
+      <c r="B398" s="17" t="s">
+        <v>909</v>
+      </c>
+      <c r="C398" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D398" s="17">
+        <v>2.0211713E7</v>
+      </c>
+      <c r="E398" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="F398" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G398" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H398" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I398" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K398" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="14">
+        <v>45726.5881019213</v>
+      </c>
+      <c r="B399" s="15" t="s">
+        <v>911</v>
+      </c>
+      <c r="C399" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D399" s="15">
+        <v>2.0205117E7</v>
+      </c>
+      <c r="E399" s="15" t="s">
+        <v>912</v>
+      </c>
+      <c r="F399" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G399" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H399" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I399" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K399" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="16">
+        <v>45726.599425243054</v>
+      </c>
+      <c r="B400" s="17" t="s">
+        <v>913</v>
+      </c>
+      <c r="C400" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="D400" s="17">
+        <v>2.0222326E7</v>
+      </c>
+      <c r="E400" s="17" t="s">
+        <v>914</v>
+      </c>
+      <c r="F400" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G400" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H400" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I400" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K400" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="14">
+        <v>45726.6547402662</v>
+      </c>
+      <c r="B401" s="15" t="s">
+        <v>915</v>
+      </c>
+      <c r="C401" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D401" s="15">
+        <v>2.0242838E7</v>
+      </c>
+      <c r="E401" s="15" t="s">
+        <v>916</v>
+      </c>
+      <c r="F401" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G401" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H401" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I401" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J401" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="16">
+        <v>45726.7576046412</v>
+      </c>
+      <c r="B402" s="17" t="s">
+        <v>917</v>
+      </c>
+      <c r="C402" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D402" s="17">
+        <v>2.0252122E7</v>
+      </c>
+      <c r="E402" s="17" t="s">
+        <v>918</v>
+      </c>
+      <c r="F402" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G402" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H402" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I402" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J402" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="14">
+        <v>45726.764921828704</v>
+      </c>
+      <c r="B403" s="15" t="s">
+        <v>919</v>
+      </c>
+      <c r="C403" s="15" t="s">
+        <v>920</v>
+      </c>
+      <c r="D403" s="15">
+        <v>2.0243525E7</v>
+      </c>
+      <c r="E403" s="15" t="s">
+        <v>921</v>
+      </c>
+      <c r="F403" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G403" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H403" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I403" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K403" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="16">
+        <v>45726.776789270836</v>
+      </c>
+      <c r="B404" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="C404" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="D404" s="17">
+        <v>2.0226769E7</v>
+      </c>
+      <c r="E404" s="17" t="s">
+        <v>923</v>
+      </c>
+      <c r="F404" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G404" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H404" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I404" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J404" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="14">
+        <v>45726.782007222224</v>
+      </c>
+      <c r="B405" s="15" t="s">
+        <v>924</v>
+      </c>
+      <c r="C405" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D405" s="15">
+        <v>2.0233433E7</v>
+      </c>
+      <c r="E405" s="15" t="s">
+        <v>925</v>
+      </c>
+      <c r="F405" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G405" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H405" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I405" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J405" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="20">
+        <v>45726.81177663195</v>
+      </c>
+      <c r="B406" s="21" t="s">
+        <v>926</v>
+      </c>
+      <c r="C406" s="21" t="s">
+        <v>927</v>
+      </c>
+      <c r="D406" s="21">
+        <v>2.0246428E7</v>
+      </c>
+      <c r="E406" s="21" t="s">
+        <v>928</v>
+      </c>
+      <c r="F406" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G406" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H406" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I406" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K406" s="22" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250303.xlsx
+++ b/R/data/quiz_250303.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3251" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3459" uniqueCount="984">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2798,6 +2798,171 @@
   </si>
   <si>
     <t>최윤서</t>
+  </si>
+  <si>
+    <t>tjdbs_s@naver.com</t>
+  </si>
+  <si>
+    <t>의약신소재전공</t>
+  </si>
+  <si>
+    <t>최서윤</t>
+  </si>
+  <si>
+    <t>hongbeens@gmail.com</t>
+  </si>
+  <si>
+    <t>조홍빈</t>
+  </si>
+  <si>
+    <t>monica.oh0609@gmail.com</t>
+  </si>
+  <si>
+    <t>오민선</t>
+  </si>
+  <si>
+    <t>ekzkdi12@naver.com</t>
+  </si>
+  <si>
+    <t>박정민</t>
+  </si>
+  <si>
+    <t>soyeon4966@naver.com</t>
+  </si>
+  <si>
+    <t>디지털인문예술전공</t>
+  </si>
+  <si>
+    <t>김소연</t>
+  </si>
+  <si>
+    <t>seonyeong1202@naver.com</t>
+  </si>
+  <si>
+    <t>백선영</t>
+  </si>
+  <si>
+    <t>wjdrjs0111@gmail.com</t>
+  </si>
+  <si>
+    <t>정건</t>
+  </si>
+  <si>
+    <t>sminji674@gmail.com</t>
+  </si>
+  <si>
+    <t>송민지</t>
+  </si>
+  <si>
+    <t>khhkhj@naver.com</t>
+  </si>
+  <si>
+    <t>김현학</t>
+  </si>
+  <si>
+    <t>gbsgbsgbs01@gmail.com</t>
+  </si>
+  <si>
+    <t>정경환</t>
+  </si>
+  <si>
+    <t>jihyunkim917@gmail.com</t>
+  </si>
+  <si>
+    <t>김지현</t>
+  </si>
+  <si>
+    <t>haeyoon205@gmail.com</t>
+  </si>
+  <si>
+    <t>정해윤</t>
+  </si>
+  <si>
+    <t>juliaj03@naver.com</t>
+  </si>
+  <si>
+    <t>정한결</t>
+  </si>
+  <si>
+    <t>choiseoungbin@gmail.com</t>
+  </si>
+  <si>
+    <t>최승빈</t>
+  </si>
+  <si>
+    <t>a01024558927@gmail.com</t>
+  </si>
+  <si>
+    <t>정용원</t>
+  </si>
+  <si>
+    <t>stopji209@naver.com</t>
+  </si>
+  <si>
+    <t>정지윤</t>
+  </si>
+  <si>
+    <t>20226424@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>글로벌 비즈니스학과</t>
+  </si>
+  <si>
+    <t>조재하</t>
+  </si>
+  <si>
+    <t>jinhoney05@naver.com</t>
+  </si>
+  <si>
+    <t>이진헌</t>
+  </si>
+  <si>
+    <t>bella0729@naver.com</t>
+  </si>
+  <si>
+    <t>김해원</t>
+  </si>
+  <si>
+    <t>kimin18_@naver.com</t>
+  </si>
+  <si>
+    <t>김민정</t>
+  </si>
+  <si>
+    <t>seo020815@naver.com</t>
+  </si>
+  <si>
+    <t>정보과학대/빅데이터</t>
+  </si>
+  <si>
+    <t>ysw201200@gmail.com</t>
+  </si>
+  <si>
+    <t>이윤서</t>
+  </si>
+  <si>
+    <t>cara3364@naver.com</t>
+  </si>
+  <si>
+    <t>최수연</t>
+  </si>
+  <si>
+    <t>rlaqufl1234@naver.com</t>
+  </si>
+  <si>
+    <t>김벼리</t>
+  </si>
+  <si>
+    <t>22berthak@naver.com</t>
+  </si>
+  <si>
+    <t>강유진</t>
+  </si>
+  <si>
+    <t>minbh5642@gmail.com</t>
+  </si>
+  <si>
+    <t>민병현</t>
   </si>
 </sst>
 </file>
@@ -3130,7 +3295,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K406" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K432" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -16333,35 +16498,867 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="20">
+      <c r="A406" s="16">
         <v>45726.81177663195</v>
       </c>
-      <c r="B406" s="21" t="s">
+      <c r="B406" s="17" t="s">
         <v>926</v>
       </c>
-      <c r="C406" s="21" t="s">
+      <c r="C406" s="17" t="s">
         <v>927</v>
       </c>
-      <c r="D406" s="21">
+      <c r="D406" s="17">
         <v>2.0246428E7</v>
       </c>
-      <c r="E406" s="21" t="s">
+      <c r="E406" s="17" t="s">
         <v>928</v>
       </c>
-      <c r="F406" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G406" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H406" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I406" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K406" s="22" t="s">
+      <c r="F406" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G406" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H406" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I406" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K406" s="19" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="14">
+        <v>45726.864616817125</v>
+      </c>
+      <c r="B407" s="15" t="s">
+        <v>929</v>
+      </c>
+      <c r="C407" s="15" t="s">
+        <v>930</v>
+      </c>
+      <c r="D407" s="15">
+        <v>2.0246644E7</v>
+      </c>
+      <c r="E407" s="15" t="s">
+        <v>931</v>
+      </c>
+      <c r="F407" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G407" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H407" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I407" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K407" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="16">
+        <v>45726.87003826389</v>
+      </c>
+      <c r="B408" s="17" t="s">
+        <v>932</v>
+      </c>
+      <c r="C408" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="D408" s="17">
+        <v>2.0243255E7</v>
+      </c>
+      <c r="E408" s="17" t="s">
+        <v>933</v>
+      </c>
+      <c r="F408" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G408" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H408" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I408" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K408" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="14">
+        <v>45726.887119085644</v>
+      </c>
+      <c r="B409" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="C409" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D409" s="15">
+        <v>2.0231618E7</v>
+      </c>
+      <c r="E409" s="15" t="s">
+        <v>935</v>
+      </c>
+      <c r="F409" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G409" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H409" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I409" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J409" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="16">
+        <v>45726.94202858796</v>
+      </c>
+      <c r="B410" s="17" t="s">
+        <v>936</v>
+      </c>
+      <c r="C410" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D410" s="17">
+        <v>2.024296E7</v>
+      </c>
+      <c r="E410" s="17" t="s">
+        <v>937</v>
+      </c>
+      <c r="F410" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G410" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H410" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I410" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J410" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="14">
+        <v>45726.95576890046</v>
+      </c>
+      <c r="B411" s="15" t="s">
+        <v>938</v>
+      </c>
+      <c r="C411" s="15" t="s">
+        <v>939</v>
+      </c>
+      <c r="D411" s="15">
+        <v>2.0241705E7</v>
+      </c>
+      <c r="E411" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="F411" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G411" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H411" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I411" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J411" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="16">
+        <v>45726.9573512037</v>
+      </c>
+      <c r="B412" s="17" t="s">
+        <v>941</v>
+      </c>
+      <c r="C412" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D412" s="17">
+        <v>2.0217026E7</v>
+      </c>
+      <c r="E412" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="F412" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G412" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H412" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I412" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K412" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="14">
+        <v>45726.96390122685</v>
+      </c>
+      <c r="B413" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="C413" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D413" s="15">
+        <v>2.0244142E7</v>
+      </c>
+      <c r="E413" s="15" t="s">
+        <v>944</v>
+      </c>
+      <c r="F413" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G413" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H413" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I413" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J413" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="16">
+        <v>45727.007509421295</v>
+      </c>
+      <c r="B414" s="17" t="s">
+        <v>945</v>
+      </c>
+      <c r="C414" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D414" s="17">
+        <v>2.0243623E7</v>
+      </c>
+      <c r="E414" s="17" t="s">
+        <v>946</v>
+      </c>
+      <c r="F414" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G414" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H414" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I414" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K414" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="14">
+        <v>45727.01274740741</v>
+      </c>
+      <c r="B415" s="15" t="s">
+        <v>947</v>
+      </c>
+      <c r="C415" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D415" s="15">
+        <v>2.0192854E7</v>
+      </c>
+      <c r="E415" s="15" t="s">
+        <v>948</v>
+      </c>
+      <c r="F415" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G415" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H415" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I415" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J415" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="16">
+        <v>45727.117665682876</v>
+      </c>
+      <c r="B416" s="17" t="s">
+        <v>949</v>
+      </c>
+      <c r="C416" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="D416" s="17">
+        <v>2.0256773E7</v>
+      </c>
+      <c r="E416" s="17" t="s">
+        <v>950</v>
+      </c>
+      <c r="F416" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G416" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H416" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I416" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J416" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="14">
+        <v>45727.41233011574</v>
+      </c>
+      <c r="B417" s="15" t="s">
+        <v>951</v>
+      </c>
+      <c r="C417" s="15" t="s">
+        <v>785</v>
+      </c>
+      <c r="D417" s="15">
+        <v>2.0241024E7</v>
+      </c>
+      <c r="E417" s="15" t="s">
+        <v>952</v>
+      </c>
+      <c r="F417" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G417" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H417" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I417" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J417" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="16">
+        <v>45727.457419548606</v>
+      </c>
+      <c r="B418" s="17" t="s">
+        <v>953</v>
+      </c>
+      <c r="C418" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D418" s="17">
+        <v>2.0241093E7</v>
+      </c>
+      <c r="E418" s="17" t="s">
+        <v>954</v>
+      </c>
+      <c r="F418" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G418" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H418" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I418" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K418" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="14">
+        <v>45727.53116428241</v>
+      </c>
+      <c r="B419" s="15" t="s">
+        <v>955</v>
+      </c>
+      <c r="C419" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="D419" s="15">
+        <v>2.0243954E7</v>
+      </c>
+      <c r="E419" s="15" t="s">
+        <v>956</v>
+      </c>
+      <c r="F419" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G419" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H419" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I419" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J419" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="16">
+        <v>45727.547167916666</v>
+      </c>
+      <c r="B420" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="C420" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D420" s="17">
+        <v>2.0243429E7</v>
+      </c>
+      <c r="E420" s="17" t="s">
+        <v>958</v>
+      </c>
+      <c r="F420" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G420" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H420" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I420" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K420" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="14">
+        <v>45727.56307694444</v>
+      </c>
+      <c r="B421" s="15" t="s">
+        <v>959</v>
+      </c>
+      <c r="C421" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D421" s="15">
+        <v>2.0242236E7</v>
+      </c>
+      <c r="E421" s="15" t="s">
+        <v>960</v>
+      </c>
+      <c r="F421" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G421" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H421" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I421" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J421" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="16">
+        <v>45727.57574673611</v>
+      </c>
+      <c r="B422" s="17" t="s">
+        <v>961</v>
+      </c>
+      <c r="C422" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D422" s="17">
+        <v>2.0227074E7</v>
+      </c>
+      <c r="E422" s="17" t="s">
+        <v>962</v>
+      </c>
+      <c r="F422" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G422" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H422" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I422" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J422" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="14">
+        <v>45727.59537858797</v>
+      </c>
+      <c r="B423" s="15" t="s">
+        <v>963</v>
+      </c>
+      <c r="C423" s="15" t="s">
+        <v>964</v>
+      </c>
+      <c r="D423" s="15">
+        <v>2.0226424E7</v>
+      </c>
+      <c r="E423" s="15" t="s">
+        <v>965</v>
+      </c>
+      <c r="F423" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G423" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H423" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I423" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K423" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="16">
+        <v>45727.598611249996</v>
+      </c>
+      <c r="B424" s="17" t="s">
+        <v>966</v>
+      </c>
+      <c r="C424" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D424" s="17">
+        <v>2.0253241E7</v>
+      </c>
+      <c r="E424" s="17" t="s">
+        <v>967</v>
+      </c>
+      <c r="F424" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G424" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H424" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I424" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J424" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="14">
+        <v>45727.59990925926</v>
+      </c>
+      <c r="B425" s="15" t="s">
+        <v>968</v>
+      </c>
+      <c r="C425" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D425" s="15">
+        <v>2.0246231E7</v>
+      </c>
+      <c r="E425" s="15" t="s">
+        <v>969</v>
+      </c>
+      <c r="F425" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G425" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H425" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I425" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K425" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="16">
+        <v>45727.62317685185</v>
+      </c>
+      <c r="B426" s="17" t="s">
+        <v>970</v>
+      </c>
+      <c r="C426" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D426" s="17">
+        <v>2.0243406E7</v>
+      </c>
+      <c r="E426" s="17" t="s">
+        <v>971</v>
+      </c>
+      <c r="F426" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G426" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H426" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I426" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J426" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="14">
+        <v>45727.69781686342</v>
+      </c>
+      <c r="B427" s="15" t="s">
+        <v>972</v>
+      </c>
+      <c r="C427" s="15" t="s">
+        <v>973</v>
+      </c>
+      <c r="D427" s="15">
+        <v>2.0215135E7</v>
+      </c>
+      <c r="E427" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="F427" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G427" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H427" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I427" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K427" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="16">
+        <v>45727.72004501158</v>
+      </c>
+      <c r="B428" s="17" t="s">
+        <v>974</v>
+      </c>
+      <c r="C428" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D428" s="17">
+        <v>2.0212556E7</v>
+      </c>
+      <c r="E428" s="17" t="s">
+        <v>975</v>
+      </c>
+      <c r="F428" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G428" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H428" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I428" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J428" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="14">
+        <v>45727.74157752315</v>
+      </c>
+      <c r="B429" s="15" t="s">
+        <v>976</v>
+      </c>
+      <c r="C429" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D429" s="15">
+        <v>2.0246295E7</v>
+      </c>
+      <c r="E429" s="15" t="s">
+        <v>977</v>
+      </c>
+      <c r="F429" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G429" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H429" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I429" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J429" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="16">
+        <v>45727.81231603009</v>
+      </c>
+      <c r="B430" s="17" t="s">
+        <v>978</v>
+      </c>
+      <c r="C430" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="D430" s="17">
+        <v>2.0212918E7</v>
+      </c>
+      <c r="E430" s="17" t="s">
+        <v>979</v>
+      </c>
+      <c r="F430" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G430" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H430" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I430" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J430" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="14">
+        <v>45727.85233098379</v>
+      </c>
+      <c r="B431" s="15" t="s">
+        <v>980</v>
+      </c>
+      <c r="C431" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D431" s="15">
+        <v>2.0246401E7</v>
+      </c>
+      <c r="E431" s="15" t="s">
+        <v>981</v>
+      </c>
+      <c r="F431" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G431" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H431" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I431" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K431" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="20">
+        <v>45727.854493182866</v>
+      </c>
+      <c r="B432" s="21" t="s">
+        <v>982</v>
+      </c>
+      <c r="C432" s="21" t="s">
+        <v>785</v>
+      </c>
+      <c r="D432" s="21">
+        <v>2.0251036E7</v>
+      </c>
+      <c r="E432" s="21" t="s">
+        <v>983</v>
+      </c>
+      <c r="F432" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G432" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H432" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I432" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K432" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250303.xlsx
+++ b/R/data/quiz_250303.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3459" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3523" uniqueCount="1002">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2963,6 +2963,60 @@
   </si>
   <si>
     <t>민병현</t>
+  </si>
+  <si>
+    <t>kar0173@naver.com</t>
+  </si>
+  <si>
+    <t>최승민</t>
+  </si>
+  <si>
+    <t>icefly1007@naver.com</t>
+  </si>
+  <si>
+    <t>우현지</t>
+  </si>
+  <si>
+    <t>20235110@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>고유빈</t>
+  </si>
+  <si>
+    <t>bluelemon051106@naver.com</t>
+  </si>
+  <si>
+    <t>신정민</t>
+  </si>
+  <si>
+    <t>castle@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>배은성</t>
+  </si>
+  <si>
+    <t>kec0705@naver.com</t>
+  </si>
+  <si>
+    <t>인공지능융합학부 - AI의료</t>
+  </si>
+  <si>
+    <t>이은영</t>
+  </si>
+  <si>
+    <t>storybjy11@naver.com</t>
+  </si>
+  <si>
+    <t>박기원</t>
+  </si>
+  <si>
+    <t>huhjunwoo0@Gmail.com</t>
+  </si>
+  <si>
+    <t>디지털미디어콘텐츠학부</t>
+  </si>
+  <si>
+    <t>허준우</t>
   </si>
 </sst>
 </file>
@@ -2993,7 +3047,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -3149,25 +3203,11 @@
         <color rgb="FF442F65"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3234,9 +3274,6 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3295,7 +3332,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K432" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K440" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -17330,35 +17367,291 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="20">
+      <c r="A432" s="16">
         <v>45727.854493182866</v>
       </c>
-      <c r="B432" s="21" t="s">
+      <c r="B432" s="17" t="s">
         <v>982</v>
       </c>
-      <c r="C432" s="21" t="s">
+      <c r="C432" s="17" t="s">
         <v>785</v>
       </c>
-      <c r="D432" s="21">
+      <c r="D432" s="17">
         <v>2.0251036E7</v>
       </c>
-      <c r="E432" s="21" t="s">
+      <c r="E432" s="17" t="s">
         <v>983</v>
       </c>
-      <c r="F432" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G432" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H432" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I432" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K432" s="22" t="s">
+      <c r="F432" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G432" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H432" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I432" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K432" s="19" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="14">
+        <v>45727.876810104164</v>
+      </c>
+      <c r="B433" s="15" t="s">
+        <v>984</v>
+      </c>
+      <c r="C433" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="D433" s="15">
+        <v>2.0202362E7</v>
+      </c>
+      <c r="E433" s="15" t="s">
+        <v>985</v>
+      </c>
+      <c r="F433" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G433" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H433" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I433" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K433" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="16">
+        <v>45727.890230324076</v>
+      </c>
+      <c r="B434" s="17" t="s">
+        <v>986</v>
+      </c>
+      <c r="C434" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D434" s="17">
+        <v>2.0242727E7</v>
+      </c>
+      <c r="E434" s="17" t="s">
+        <v>987</v>
+      </c>
+      <c r="F434" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G434" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H434" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I434" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J434" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="14">
+        <v>45727.905450578706</v>
+      </c>
+      <c r="B435" s="15" t="s">
+        <v>988</v>
+      </c>
+      <c r="C435" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D435" s="15">
+        <v>2.023511E7</v>
+      </c>
+      <c r="E435" s="15" t="s">
+        <v>989</v>
+      </c>
+      <c r="F435" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G435" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H435" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I435" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K435" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="16">
+        <v>45727.92663990741</v>
+      </c>
+      <c r="B436" s="17" t="s">
+        <v>990</v>
+      </c>
+      <c r="C436" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D436" s="17">
+        <v>2.0222615E7</v>
+      </c>
+      <c r="E436" s="17" t="s">
+        <v>991</v>
+      </c>
+      <c r="F436" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G436" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H436" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I436" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J436" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="14">
+        <v>45727.93037912037</v>
+      </c>
+      <c r="B437" s="15" t="s">
+        <v>992</v>
+      </c>
+      <c r="C437" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D437" s="15">
+        <v>2.0222962E7</v>
+      </c>
+      <c r="E437" s="15" t="s">
+        <v>993</v>
+      </c>
+      <c r="F437" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G437" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H437" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I437" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J437" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="16">
+        <v>45727.94676907407</v>
+      </c>
+      <c r="B438" s="17" t="s">
+        <v>994</v>
+      </c>
+      <c r="C438" s="17" t="s">
+        <v>995</v>
+      </c>
+      <c r="D438" s="17">
+        <v>2.0227161E7</v>
+      </c>
+      <c r="E438" s="17" t="s">
+        <v>996</v>
+      </c>
+      <c r="F438" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G438" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H438" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I438" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K438" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="14">
+        <v>45727.9587341088</v>
+      </c>
+      <c r="B439" s="15" t="s">
+        <v>997</v>
+      </c>
+      <c r="C439" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="D439" s="15">
+        <v>2.0191615E7</v>
+      </c>
+      <c r="E439" s="15" t="s">
+        <v>998</v>
+      </c>
+      <c r="F439" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G439" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H439" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I439" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K439" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="20">
+        <v>45728.070282037035</v>
+      </c>
+      <c r="B440" s="21" t="s">
+        <v>999</v>
+      </c>
+      <c r="C440" s="21" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D440" s="21">
+        <v>2.0246792E7</v>
+      </c>
+      <c r="E440" s="21" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F440" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G440" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H440" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I440" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J440" s="21" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250303.xlsx
+++ b/R/data/quiz_250303.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3523" uniqueCount="1002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3619" uniqueCount="1027">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -3017,6 +3017,81 @@
   </si>
   <si>
     <t>허준우</t>
+  </si>
+  <si>
+    <t>lswon9916@naver.com</t>
+  </si>
+  <si>
+    <t>이서원</t>
+  </si>
+  <si>
+    <t>hmsimlk@naver.com</t>
+  </si>
+  <si>
+    <t>홍수민</t>
+  </si>
+  <si>
+    <t>leeji77006674@gmail.com</t>
+  </si>
+  <si>
+    <t>이지원</t>
+  </si>
+  <si>
+    <t>subin051001@naver.com</t>
+  </si>
+  <si>
+    <t>송수빈</t>
+  </si>
+  <si>
+    <t>kkimsol@naver.com</t>
+  </si>
+  <si>
+    <t>김솔</t>
+  </si>
+  <si>
+    <t>chlwodlf9557@naver.com</t>
+  </si>
+  <si>
+    <t>최재일</t>
+  </si>
+  <si>
+    <t>khe1021bb@gmail.com</t>
+  </si>
+  <si>
+    <t>김하은</t>
+  </si>
+  <si>
+    <t>bogertave25@gmail.com</t>
+  </si>
+  <si>
+    <t>최지용</t>
+  </si>
+  <si>
+    <t>jysjys1006@naver.com</t>
+  </si>
+  <si>
+    <t>지예슬</t>
+  </si>
+  <si>
+    <t>fireanger0@gmail.com</t>
+  </si>
+  <si>
+    <t>AI로봇융합학과</t>
+  </si>
+  <si>
+    <t>양조은</t>
+  </si>
+  <si>
+    <t>h20241202@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>김민규</t>
+  </si>
+  <si>
+    <t>h20241217@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>원예진</t>
   </si>
 </sst>
 </file>
@@ -3332,7 +3407,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K440" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K452" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -17623,35 +17698,419 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="20">
+      <c r="A440" s="16">
         <v>45728.070282037035</v>
       </c>
-      <c r="B440" s="21" t="s">
+      <c r="B440" s="17" t="s">
         <v>999</v>
       </c>
-      <c r="C440" s="21" t="s">
+      <c r="C440" s="17" t="s">
         <v>1000</v>
       </c>
-      <c r="D440" s="21">
+      <c r="D440" s="17">
         <v>2.0246792E7</v>
       </c>
-      <c r="E440" s="21" t="s">
+      <c r="E440" s="17" t="s">
         <v>1001</v>
       </c>
-      <c r="F440" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G440" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H440" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I440" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="J440" s="21" t="s">
+      <c r="F440" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G440" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H440" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I440" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J440" s="17" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="14">
+        <v>45728.380098877315</v>
+      </c>
+      <c r="B441" s="15" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C441" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D441" s="15">
+        <v>2.0243936E7</v>
+      </c>
+      <c r="E441" s="15" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F441" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G441" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H441" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I441" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J441" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="16">
+        <v>45728.42101534722</v>
+      </c>
+      <c r="B442" s="17" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C442" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D442" s="17">
+        <v>2.0243545E7</v>
+      </c>
+      <c r="E442" s="17" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F442" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G442" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H442" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I442" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K442" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="14">
+        <v>45728.58544571759</v>
+      </c>
+      <c r="B443" s="15" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C443" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D443" s="15">
+        <v>2.0242633E7</v>
+      </c>
+      <c r="E443" s="15" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F443" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G443" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H443" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I443" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J443" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="16">
+        <v>45728.62928283565</v>
+      </c>
+      <c r="B444" s="17" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C444" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="D444" s="17">
+        <v>2.024253E7</v>
+      </c>
+      <c r="E444" s="17" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F444" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G444" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H444" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I444" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K444" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="14">
+        <v>45728.64357151621</v>
+      </c>
+      <c r="B445" s="15" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C445" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D445" s="15">
+        <v>2.0241514E7</v>
+      </c>
+      <c r="E445" s="15" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F445" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G445" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H445" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I445" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J445" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="16">
+        <v>45728.72451299768</v>
+      </c>
+      <c r="B446" s="17" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C446" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D446" s="17">
+        <v>2.0203056E7</v>
+      </c>
+      <c r="E446" s="17" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F446" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G446" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H446" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I446" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K446" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="14">
+        <v>45728.73413020834</v>
+      </c>
+      <c r="B447" s="15" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C447" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="D447" s="15">
+        <v>2.024662E7</v>
+      </c>
+      <c r="E447" s="15" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F447" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G447" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H447" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I447" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J447" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="16">
+        <v>45728.80479543981</v>
+      </c>
+      <c r="B448" s="17" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C448" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D448" s="17">
+        <v>2.0242754E7</v>
+      </c>
+      <c r="E448" s="17" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F448" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G448" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H448" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I448" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J448" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="14">
+        <v>45728.80830502315</v>
+      </c>
+      <c r="B449" s="15" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C449" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D449" s="15">
+        <v>2.0217073E7</v>
+      </c>
+      <c r="E449" s="15" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F449" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G449" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H449" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I449" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K449" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="16">
+        <v>45728.97385334491</v>
+      </c>
+      <c r="B450" s="17" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C450" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D450" s="17">
+        <v>2.0246745E7</v>
+      </c>
+      <c r="E450" s="17" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F450" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G450" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H450" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I450" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K450" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="14">
+        <v>45729.006975625</v>
+      </c>
+      <c r="B451" s="15" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C451" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D451" s="15">
+        <v>2.0241202E7</v>
+      </c>
+      <c r="E451" s="15" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F451" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G451" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H451" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I451" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J451" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="20">
+        <v>45729.00703266203</v>
+      </c>
+      <c r="B452" s="21" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C452" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D452" s="21">
+        <v>2.0241217E7</v>
+      </c>
+      <c r="E452" s="21" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F452" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G452" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H452" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I452" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J452" s="21" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250303.xlsx
+++ b/R/data/quiz_250303.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3619" uniqueCount="1027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3755" uniqueCount="1063">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -3092,6 +3092,114 @@
   </si>
   <si>
     <t>원예진</t>
+  </si>
+  <si>
+    <t>swh12q@gmail.com</t>
+  </si>
+  <si>
+    <t>글로벌경영학과</t>
+  </si>
+  <si>
+    <t>권지영</t>
+  </si>
+  <si>
+    <t>namjihk@gmail.com</t>
+  </si>
+  <si>
+    <t>남지혁</t>
+  </si>
+  <si>
+    <t>kosac99-@naver.com</t>
+  </si>
+  <si>
+    <t>김성희</t>
+  </si>
+  <si>
+    <t>minnzz118@gmail.com</t>
+  </si>
+  <si>
+    <t>서민지</t>
+  </si>
+  <si>
+    <t>juni060919@naver.com</t>
+  </si>
+  <si>
+    <t>이주은</t>
+  </si>
+  <si>
+    <t>alexwoojin17@gmail.com</t>
+  </si>
+  <si>
+    <t>차우진</t>
+  </si>
+  <si>
+    <t>ssg663927@naver.com</t>
+  </si>
+  <si>
+    <t>신성결</t>
+  </si>
+  <si>
+    <t>wkdrmsgur12345678@gmail.com</t>
+  </si>
+  <si>
+    <t>스마트IoT</t>
+  </si>
+  <si>
+    <t>장근혁</t>
+  </si>
+  <si>
+    <t>gksrjs0602@naver.com</t>
+  </si>
+  <si>
+    <t>한건희</t>
+  </si>
+  <si>
+    <t>uksongcheol@naver.com</t>
+  </si>
+  <si>
+    <t>김성철</t>
+  </si>
+  <si>
+    <t>ckdnvd!e@kakao.com</t>
+  </si>
+  <si>
+    <t>이시온</t>
+  </si>
+  <si>
+    <t>baekwondong@naver.com</t>
+  </si>
+  <si>
+    <t>백원동</t>
+  </si>
+  <si>
+    <t>20225268@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>최은임</t>
+  </si>
+  <si>
+    <t>ckgustjr0705@gmail.com</t>
+  </si>
+  <si>
+    <t>차현석</t>
+  </si>
+  <si>
+    <t>qkrwndus1117@naver.com</t>
+  </si>
+  <si>
+    <t>박주연</t>
+  </si>
+  <si>
+    <t>jiwon041202@naver.com</t>
+  </si>
+  <si>
+    <t>윤지원</t>
+  </si>
+  <si>
+    <t>3628kyl@naver.com</t>
+  </si>
+  <si>
+    <t>권혜수</t>
   </si>
 </sst>
 </file>
@@ -3122,7 +3230,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border/>
     <border>
       <left style="thin">
@@ -3255,10 +3363,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -3266,13 +3374,27 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -3282,7 +3404,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3349,6 +3471,9 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3407,7 +3532,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K452" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K469" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -18082,35 +18207,579 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="20">
+      <c r="A452" s="16">
         <v>45729.00703266203</v>
       </c>
-      <c r="B452" s="21" t="s">
+      <c r="B452" s="17" t="s">
         <v>1025</v>
       </c>
-      <c r="C452" s="21" t="s">
+      <c r="C452" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D452" s="21">
+      <c r="D452" s="17">
         <v>2.0241217E7</v>
       </c>
-      <c r="E452" s="21" t="s">
+      <c r="E452" s="17" t="s">
         <v>1026</v>
       </c>
-      <c r="F452" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G452" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H452" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I452" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="J452" s="21" t="s">
+      <c r="F452" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G452" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H452" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I452" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J452" s="17" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="14">
+        <v>45729.3803974537</v>
+      </c>
+      <c r="B453" s="15" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C453" s="15" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D453" s="15">
+        <v>2.0246403E7</v>
+      </c>
+      <c r="E453" s="15" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F453" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G453" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H453" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I453" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K453" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="16">
+        <v>45729.463549120366</v>
+      </c>
+      <c r="B454" s="17" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C454" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D454" s="17">
+        <v>2.0242944E7</v>
+      </c>
+      <c r="E454" s="17" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F454" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G454" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H454" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I454" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K454" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="14">
+        <v>45729.55779387731</v>
+      </c>
+      <c r="B455" s="15" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C455" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D455" s="15">
+        <v>2.0243407E7</v>
+      </c>
+      <c r="E455" s="15" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F455" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G455" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H455" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I455" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K455" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="16">
+        <v>45729.575806759254</v>
+      </c>
+      <c r="B456" s="17" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C456" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D456" s="17">
+        <v>2.0246923E7</v>
+      </c>
+      <c r="E456" s="17" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F456" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G456" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H456" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I456" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J456" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="14">
+        <v>45729.63885127315</v>
+      </c>
+      <c r="B457" s="15" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C457" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="D457" s="15">
+        <v>2.025394E7</v>
+      </c>
+      <c r="E457" s="15" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F457" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G457" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H457" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I457" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K457" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="16">
+        <v>45729.646424108796</v>
+      </c>
+      <c r="B458" s="17" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C458" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="D458" s="17">
+        <v>2.0243042E7</v>
+      </c>
+      <c r="E458" s="17" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F458" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G458" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H458" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I458" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K458" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="14">
+        <v>45729.691847152775</v>
+      </c>
+      <c r="B459" s="15" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C459" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="D459" s="15">
+        <v>2.0227026E7</v>
+      </c>
+      <c r="E459" s="15" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F459" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G459" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H459" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I459" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K459" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="16">
+        <v>45729.704289120375</v>
+      </c>
+      <c r="B460" s="17" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C460" s="17" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D460" s="17">
+        <v>2.024524E7</v>
+      </c>
+      <c r="E460" s="17" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F460" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G460" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H460" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I460" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K460" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="14">
+        <v>45729.71343765046</v>
+      </c>
+      <c r="B461" s="15" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C461" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D461" s="15">
+        <v>2.0242755E7</v>
+      </c>
+      <c r="E461" s="15" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F461" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G461" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H461" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I461" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J461" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="16">
+        <v>45729.73058046296</v>
+      </c>
+      <c r="B462" s="17" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C462" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D462" s="17">
+        <v>2.0192204E7</v>
+      </c>
+      <c r="E462" s="17" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F462" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G462" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H462" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I462" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J462" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="14">
+        <v>45729.85033006944</v>
+      </c>
+      <c r="B463" s="15" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C463" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D463" s="15">
+        <v>2.0212744E7</v>
+      </c>
+      <c r="E463" s="15" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F463" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G463" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H463" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I463" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J463" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="16">
+        <v>45729.88048710648</v>
+      </c>
+      <c r="B464" s="17" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C464" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D464" s="17">
+        <v>2.0203921E7</v>
+      </c>
+      <c r="E464" s="17" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F464" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G464" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H464" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I464" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J464" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="14">
+        <v>45729.89175076388</v>
+      </c>
+      <c r="B465" s="15" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C465" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="D465" s="15">
+        <v>2.0225268E7</v>
+      </c>
+      <c r="E465" s="15" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F465" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G465" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H465" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I465" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J465" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="16">
+        <v>45729.93076827546</v>
+      </c>
+      <c r="B466" s="17" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C466" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D466" s="17">
+        <v>2.024629E7</v>
+      </c>
+      <c r="E466" s="17" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F466" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G466" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H466" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I466" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J466" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="14">
+        <v>45729.96864390046</v>
+      </c>
+      <c r="B467" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C467" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D467" s="15">
+        <v>2.0243513E7</v>
+      </c>
+      <c r="E467" s="15" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F467" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G467" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H467" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I467" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J467" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="16">
+        <v>45729.99197512731</v>
+      </c>
+      <c r="B468" s="17" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C468" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D468" s="17">
+        <v>2.0252225E7</v>
+      </c>
+      <c r="E468" s="17" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F468" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G468" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H468" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I468" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J468" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="20">
+        <v>45730.028995914356</v>
+      </c>
+      <c r="B469" s="21" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C469" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D469" s="21">
+        <v>2.0242605E7</v>
+      </c>
+      <c r="E469" s="21" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F469" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G469" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H469" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I469" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K469" s="22" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250303.xlsx
+++ b/R/data/quiz_250303.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3755" uniqueCount="1063">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4003" uniqueCount="1123">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -3200,6 +3200,186 @@
   </si>
   <si>
     <t>권혜수</t>
+  </si>
+  <si>
+    <t>cara0070322@naver.com</t>
+  </si>
+  <si>
+    <t>신성민</t>
+  </si>
+  <si>
+    <t>choiy617@naver.com</t>
+  </si>
+  <si>
+    <t>촤원찬</t>
+  </si>
+  <si>
+    <t>skrud030405@naver.com</t>
+  </si>
+  <si>
+    <t>김나경</t>
+  </si>
+  <si>
+    <t>bellia0321@naver.com</t>
+  </si>
+  <si>
+    <t>손가연</t>
+  </si>
+  <si>
+    <t>sinsujin0121@naver.com</t>
+  </si>
+  <si>
+    <t>신수진</t>
+  </si>
+  <si>
+    <t>kimfoxmj@gmail.com</t>
+  </si>
+  <si>
+    <t>dfhirtywk@gmail.com</t>
+  </si>
+  <si>
+    <t>최세현</t>
+  </si>
+  <si>
+    <t>20215177@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>신승훈</t>
+  </si>
+  <si>
+    <t>hyeri051119@naver.com</t>
+  </si>
+  <si>
+    <t>서혜리</t>
+  </si>
+  <si>
+    <t>es187019@gmail.com</t>
+  </si>
+  <si>
+    <t>김현빈</t>
+  </si>
+  <si>
+    <t>dltjdgns040528@naver.com</t>
+  </si>
+  <si>
+    <t>이성훈</t>
+  </si>
+  <si>
+    <t>hansi00721@gmail.com</t>
+  </si>
+  <si>
+    <t>한상익</t>
+  </si>
+  <si>
+    <t>g01086348696@gmail.com</t>
+  </si>
+  <si>
+    <t>박선근</t>
+  </si>
+  <si>
+    <t>soyang4040@naver.com</t>
+  </si>
+  <si>
+    <t>김상교</t>
+  </si>
+  <si>
+    <t>jonghyeogc126@gmail.com</t>
+  </si>
+  <si>
+    <t>최종혁</t>
+  </si>
+  <si>
+    <t>leeds44@naver.com</t>
+  </si>
+  <si>
+    <t>빅데이터과</t>
+  </si>
+  <si>
+    <t>이동수</t>
+  </si>
+  <si>
+    <t>ksl100101@gmail.com</t>
+  </si>
+  <si>
+    <t>김사랑</t>
+  </si>
+  <si>
+    <t>dhhhxh273@naver.com</t>
+  </si>
+  <si>
+    <t>최서정</t>
+  </si>
+  <si>
+    <t>juseung1449@naver.com</t>
+  </si>
+  <si>
+    <t>이주승</t>
+  </si>
+  <si>
+    <t>scb0897@naver.com</t>
+  </si>
+  <si>
+    <t>신채빈</t>
+  </si>
+  <si>
+    <t>lamsys@naver.com</t>
+  </si>
+  <si>
+    <t>정시효</t>
+  </si>
+  <si>
+    <t>seahorse93076714@gmail.com</t>
+  </si>
+  <si>
+    <t>ahyeon8650@naver.com</t>
+  </si>
+  <si>
+    <t>서아현</t>
+  </si>
+  <si>
+    <t>sdg3729@naver.com</t>
+  </si>
+  <si>
+    <t>노윤희</t>
+  </si>
+  <si>
+    <t>taehoon9466@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체-디스플레이스쿨</t>
+  </si>
+  <si>
+    <t>염태훈</t>
+  </si>
+  <si>
+    <t>danieloh1216@gmail.com</t>
+  </si>
+  <si>
+    <t>오주람</t>
+  </si>
+  <si>
+    <t>kimjnuadad@naver.com</t>
+  </si>
+  <si>
+    <t>2005tree@gmail.com</t>
+  </si>
+  <si>
+    <t>신영욱</t>
+  </si>
+  <si>
+    <t>hours00@naver.com</t>
+  </si>
+  <si>
+    <t>우수민</t>
+  </si>
+  <si>
+    <t>janghs476@gmail.com</t>
+  </si>
+  <si>
+    <t>장현서</t>
+  </si>
+  <si>
+    <t>kimminjung6615@hanmail.net</t>
   </si>
 </sst>
 </file>
@@ -3230,7 +3410,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -3363,10 +3543,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -3374,27 +3554,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -3404,7 +3570,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3471,9 +3637,6 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3532,7 +3695,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K469" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K500" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -18751,35 +18914,1027 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="20">
+      <c r="A469" s="14">
         <v>45730.028995914356</v>
       </c>
-      <c r="B469" s="21" t="s">
+      <c r="B469" s="15" t="s">
         <v>1061</v>
       </c>
-      <c r="C469" s="21" t="s">
+      <c r="C469" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D469" s="21">
+      <c r="D469" s="15">
         <v>2.0242605E7</v>
       </c>
-      <c r="E469" s="21" t="s">
+      <c r="E469" s="15" t="s">
         <v>1062</v>
       </c>
-      <c r="F469" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G469" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H469" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I469" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K469" s="22" t="s">
+      <c r="F469" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G469" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H469" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I469" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K469" s="18" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="16">
+        <v>45730.38578003472</v>
+      </c>
+      <c r="B470" s="17" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C470" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="D470" s="17">
+        <v>2.024674E7</v>
+      </c>
+      <c r="E470" s="17" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F470" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G470" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H470" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I470" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K470" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="14">
+        <v>45730.553035370365</v>
+      </c>
+      <c r="B471" s="15" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C471" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D471" s="15">
+        <v>2.0231097E7</v>
+      </c>
+      <c r="E471" s="15" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F471" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G471" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H471" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I471" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J471" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="16">
+        <v>45730.67236680556</v>
+      </c>
+      <c r="B472" s="17" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C472" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D472" s="17">
+        <v>2.0227146E7</v>
+      </c>
+      <c r="E472" s="17" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F472" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G472" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H472" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I472" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K472" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="14">
+        <v>45730.75326184028</v>
+      </c>
+      <c r="B473" s="15" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C473" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D473" s="15">
+        <v>2.023297E7</v>
+      </c>
+      <c r="E473" s="15" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F473" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G473" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H473" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I473" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J473" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="16">
+        <v>45730.79732383102</v>
+      </c>
+      <c r="B474" s="17" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C474" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D474" s="17">
+        <v>2.0242622E7</v>
+      </c>
+      <c r="E474" s="17" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F474" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G474" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H474" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I474" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K474" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="14">
+        <v>45730.83329895833</v>
+      </c>
+      <c r="B475" s="15" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C475" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D475" s="15">
+        <v>2.0232205E7</v>
+      </c>
+      <c r="E475" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="F475" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G475" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H475" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I475" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J475" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="16">
+        <v>45730.852388680556</v>
+      </c>
+      <c r="B476" s="17" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C476" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D476" s="17">
+        <v>2.0241105E7</v>
+      </c>
+      <c r="E476" s="17" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F476" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G476" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H476" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I476" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K476" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="14">
+        <v>45730.889154351855</v>
+      </c>
+      <c r="B477" s="15" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C477" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="D477" s="15">
+        <v>2.0215177E7</v>
+      </c>
+      <c r="E477" s="15" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F477" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G477" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H477" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I477" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J477" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="16">
+        <v>45730.92737469907</v>
+      </c>
+      <c r="B478" s="17" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C478" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D478" s="17">
+        <v>2.0243515E7</v>
+      </c>
+      <c r="E478" s="17" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F478" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G478" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H478" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I478" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J478" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="14">
+        <v>45730.933099120375</v>
+      </c>
+      <c r="B479" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C479" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D479" s="15">
+        <v>2.0242715E7</v>
+      </c>
+      <c r="E479" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F479" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G479" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H479" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I479" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K479" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="16">
+        <v>45730.97455068287</v>
+      </c>
+      <c r="B480" s="17" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C480" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="D480" s="17">
+        <v>2.0231716E7</v>
+      </c>
+      <c r="E480" s="17" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F480" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G480" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H480" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I480" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J480" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="14">
+        <v>45731.04812827546</v>
+      </c>
+      <c r="B481" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C481" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D481" s="15">
+        <v>2.0215266E7</v>
+      </c>
+      <c r="E481" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F481" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G481" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H481" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I481" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K481" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="16">
+        <v>45731.28510421296</v>
+      </c>
+      <c r="B482" s="17" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C482" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D482" s="17">
+        <v>2.0242717E7</v>
+      </c>
+      <c r="E482" s="17" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F482" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G482" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H482" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I482" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J482" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="14">
+        <v>45731.33641802083</v>
+      </c>
+      <c r="B483" s="15" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C483" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D483" s="15">
+        <v>2.021271E7</v>
+      </c>
+      <c r="E483" s="15" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F483" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G483" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H483" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I483" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J483" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="16">
+        <v>45731.564939895834</v>
+      </c>
+      <c r="B484" s="17" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C484" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="D484" s="17">
+        <v>2.0211537E7</v>
+      </c>
+      <c r="E484" s="17" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F484" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G484" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H484" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I484" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J484" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="14">
+        <v>45731.56804790509</v>
+      </c>
+      <c r="B485" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C485" s="15" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D485" s="15">
+        <v>2.0215202E7</v>
+      </c>
+      <c r="E485" s="15" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F485" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G485" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H485" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I485" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K485" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="16">
+        <v>45731.579625196755</v>
+      </c>
+      <c r="B486" s="17" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C486" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="D486" s="17">
+        <v>2.024231E7</v>
+      </c>
+      <c r="E486" s="17" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F486" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G486" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H486" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I486" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K486" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="14">
+        <v>45731.60968109954</v>
+      </c>
+      <c r="B487" s="15" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C487" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D487" s="15">
+        <v>2.0213639E7</v>
+      </c>
+      <c r="E487" s="15" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F487" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G487" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H487" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I487" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K487" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="16">
+        <v>45731.60975217592</v>
+      </c>
+      <c r="B488" s="17" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C488" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D488" s="17">
+        <v>2.0203726E7</v>
+      </c>
+      <c r="E488" s="17" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F488" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G488" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H488" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I488" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J488" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="14">
+        <v>45731.66409766204</v>
+      </c>
+      <c r="B489" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C489" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D489" s="15">
+        <v>2.0243521E7</v>
+      </c>
+      <c r="E489" s="15" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F489" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G489" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H489" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I489" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J489" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="16">
+        <v>45731.69833557871</v>
+      </c>
+      <c r="B490" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C490" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D490" s="17">
+        <v>2.0243427E7</v>
+      </c>
+      <c r="E490" s="17" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F490" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G490" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H490" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I490" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J490" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="14">
+        <v>45731.75520658564</v>
+      </c>
+      <c r="B491" s="15" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C491" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D491" s="15">
+        <v>2.0241229E7</v>
+      </c>
+      <c r="E491" s="15" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F491" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G491" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H491" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I491" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K491" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="16">
+        <v>45731.773276712964</v>
+      </c>
+      <c r="B492" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C492" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D492" s="17">
+        <v>2.0223824E7</v>
+      </c>
+      <c r="E492" s="17" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F492" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G492" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H492" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I492" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J492" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="14">
+        <v>45731.7763017824</v>
+      </c>
+      <c r="B493" s="15" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C493" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="D493" s="15">
+        <v>2.021515E7</v>
+      </c>
+      <c r="E493" s="15" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F493" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G493" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H493" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I493" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K493" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="16">
+        <v>45731.82726081018</v>
+      </c>
+      <c r="B494" s="17" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C494" s="17" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D494" s="17">
+        <v>2.0243331E7</v>
+      </c>
+      <c r="E494" s="17" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F494" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G494" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H494" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="I494" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J494" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="14">
+        <v>45731.90668827546</v>
+      </c>
+      <c r="B495" s="15" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C495" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D495" s="15">
+        <v>2.0243522E7</v>
+      </c>
+      <c r="E495" s="15" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F495" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G495" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H495" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I495" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J495" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="16">
+        <v>45731.93549163194</v>
+      </c>
+      <c r="B496" s="17" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C496" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D496" s="17">
+        <v>2.0241201E7</v>
+      </c>
+      <c r="E496" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="F496" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G496" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H496" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I496" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K496" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="14">
+        <v>45731.94106118055</v>
+      </c>
+      <c r="B497" s="15" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C497" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D497" s="15">
+        <v>2.024625E7</v>
+      </c>
+      <c r="E497" s="15" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F497" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G497" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H497" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I497" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K497" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="16">
+        <v>45731.95566180555</v>
+      </c>
+      <c r="B498" s="17" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C498" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D498" s="17">
+        <v>2.0246257E7</v>
+      </c>
+      <c r="E498" s="17" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F498" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G498" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H498" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I498" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J498" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="14">
+        <v>45731.968429201384</v>
+      </c>
+      <c r="B499" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C499" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D499" s="15">
+        <v>2.0245245E7</v>
+      </c>
+      <c r="E499" s="15" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F499" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G499" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H499" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I499" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K499" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="20">
+        <v>45731.974920451394</v>
+      </c>
+      <c r="B500" s="21" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C500" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="D500" s="21">
+        <v>2.0241012E7</v>
+      </c>
+      <c r="E500" s="21" t="s">
+        <v>971</v>
+      </c>
+      <c r="F500" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G500" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H500" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I500" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J500" s="21" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250303.xlsx
+++ b/R/data/quiz_250303.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4003" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4659" uniqueCount="1284">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -3380,6 +3380,489 @@
   </si>
   <si>
     <t>kimminjung6615@hanmail.net</t>
+  </si>
+  <si>
+    <t>ehdcks3444@naver.com</t>
+  </si>
+  <si>
+    <t>김동찬</t>
+  </si>
+  <si>
+    <t>qusdnwls12@gmail.com</t>
+  </si>
+  <si>
+    <t>변우진</t>
+  </si>
+  <si>
+    <t>solyooncho@gmail.com</t>
+  </si>
+  <si>
+    <t>조윤솔</t>
+  </si>
+  <si>
+    <t>jhbbjshb-djnd@naver.com</t>
+  </si>
+  <si>
+    <t>성지민</t>
+  </si>
+  <si>
+    <t>hyub1509@naver.com</t>
+  </si>
+  <si>
+    <t>이준협</t>
+  </si>
+  <si>
+    <t>dustj9033@gmail.com</t>
+  </si>
+  <si>
+    <t>고연서</t>
+  </si>
+  <si>
+    <t>hansoomin1108@gmail.com</t>
+  </si>
+  <si>
+    <t>디지털금융정보과</t>
+  </si>
+  <si>
+    <t>성수민</t>
+  </si>
+  <si>
+    <t>20226614@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>김태현</t>
+  </si>
+  <si>
+    <t>seojingwon8@gmail.com</t>
+  </si>
+  <si>
+    <t>권서진</t>
+  </si>
+  <si>
+    <t>20241726@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>이효린</t>
+  </si>
+  <si>
+    <t>capjjjmj@naver.com</t>
+  </si>
+  <si>
+    <t>전민정</t>
+  </si>
+  <si>
+    <t>danggun06@naver.com</t>
+  </si>
+  <si>
+    <t>황다은</t>
+  </si>
+  <si>
+    <t>xogns7149@naver.com</t>
+  </si>
+  <si>
+    <t>경역학과</t>
+  </si>
+  <si>
+    <t>김태욱</t>
+  </si>
+  <si>
+    <t>soeun7443@naver.com</t>
+  </si>
+  <si>
+    <t>박소은</t>
+  </si>
+  <si>
+    <t>jenny_0603@naver.com</t>
+  </si>
+  <si>
+    <t>이지수</t>
+  </si>
+  <si>
+    <t>yangsj0626@gmail.com</t>
+  </si>
+  <si>
+    <t>양선준</t>
+  </si>
+  <si>
+    <t>kyjgirin@naver.com</t>
+  </si>
+  <si>
+    <t>의약신소재</t>
+  </si>
+  <si>
+    <t>권예주</t>
+  </si>
+  <si>
+    <t>000727yjh@naver.com</t>
+  </si>
+  <si>
+    <t>윤종현</t>
+  </si>
+  <si>
+    <t>ratso6113@gmail.com</t>
+  </si>
+  <si>
+    <t>이소연</t>
+  </si>
+  <si>
+    <t>god303086@gmail.com</t>
+  </si>
+  <si>
+    <t>디지털미디언콘텐츠학과</t>
+  </si>
+  <si>
+    <t>남궁연희</t>
+  </si>
+  <si>
+    <t>20202514@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>김윤아</t>
+  </si>
+  <si>
+    <t>moonsy06@naver.com</t>
+  </si>
+  <si>
+    <t>문소연</t>
+  </si>
+  <si>
+    <t>yky9430@naver.com</t>
+  </si>
+  <si>
+    <t>유가영</t>
+  </si>
+  <si>
+    <t>kimminwoo78901@gmail.com</t>
+  </si>
+  <si>
+    <t>김민우</t>
+  </si>
+  <si>
+    <t>chrisjuice@naver.com</t>
+  </si>
+  <si>
+    <t>한수민</t>
+  </si>
+  <si>
+    <t>kiki01111@naver.com</t>
+  </si>
+  <si>
+    <t>노기훈</t>
+  </si>
+  <si>
+    <t>aod1574@naver.com</t>
+  </si>
+  <si>
+    <t>맹은지</t>
+  </si>
+  <si>
+    <t>bjfcu7@gmail.com</t>
+  </si>
+  <si>
+    <t>김채연</t>
+  </si>
+  <si>
+    <t>pgueue110@gmail.com</t>
+  </si>
+  <si>
+    <t>정다영</t>
+  </si>
+  <si>
+    <t>jae2001830@naver.com</t>
+  </si>
+  <si>
+    <t>이재홍</t>
+  </si>
+  <si>
+    <t>seojungbin050928@naver.com</t>
+  </si>
+  <si>
+    <t>서정빈</t>
+  </si>
+  <si>
+    <t>lee_tmdgus@naver.com</t>
+  </si>
+  <si>
+    <t>이승현</t>
+  </si>
+  <si>
+    <t>h20241235@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>정채원</t>
+  </si>
+  <si>
+    <t>imjustdaeunnn@gmail.com</t>
+  </si>
+  <si>
+    <t>정다은</t>
+  </si>
+  <si>
+    <t>tldkwhgsl@gmail.com</t>
+  </si>
+  <si>
+    <t>최다온</t>
+  </si>
+  <si>
+    <t>ssw29772977@gmail.com</t>
+  </si>
+  <si>
+    <t>성승원</t>
+  </si>
+  <si>
+    <t>woojinkim0518@naver.com</t>
+  </si>
+  <si>
+    <t>김우진</t>
+  </si>
+  <si>
+    <t>kseoj123@naver.com</t>
+  </si>
+  <si>
+    <t>김서진</t>
+  </si>
+  <si>
+    <t>jinyeob919@gmail.com</t>
+  </si>
+  <si>
+    <t>김진엽</t>
+  </si>
+  <si>
+    <t>lim48664401@gmail.com</t>
+  </si>
+  <si>
+    <t>임동욱</t>
+  </si>
+  <si>
+    <t>kjh217196@naver.com</t>
+  </si>
+  <si>
+    <t>ohyegon050824@gmail.com</t>
+  </si>
+  <si>
+    <t>오예건</t>
+  </si>
+  <si>
+    <t>selliakim@gmail.com</t>
+  </si>
+  <si>
+    <t>김수아</t>
+  </si>
+  <si>
+    <t>jiwoo1656@naver.com</t>
+  </si>
+  <si>
+    <t>정지우</t>
+  </si>
+  <si>
+    <t>rhdbswn01@naver.com</t>
+  </si>
+  <si>
+    <t>언론방송융합미디어학과</t>
+  </si>
+  <si>
+    <t>고윤주</t>
+  </si>
+  <si>
+    <t>gin050302@naver.com</t>
+  </si>
+  <si>
+    <t>김현정</t>
+  </si>
+  <si>
+    <t>eshan0401@gmail.com</t>
+  </si>
+  <si>
+    <t>한은성</t>
+  </si>
+  <si>
+    <t>cntmddl1@naver.com</t>
+  </si>
+  <si>
+    <t>추승이</t>
+  </si>
+  <si>
+    <t>kmkben@naver.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">영어영문학과 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">장서연 </t>
+  </si>
+  <si>
+    <t>jaeyoon1163@naver.com</t>
+  </si>
+  <si>
+    <t>정재윤</t>
+  </si>
+  <si>
+    <t>amazing7124@naver.com</t>
+  </si>
+  <si>
+    <t>서준호</t>
+  </si>
+  <si>
+    <t>kangryeonghyeon1234@gmail.com</t>
+  </si>
+  <si>
+    <t>강령현</t>
+  </si>
+  <si>
+    <t>djfvks@naver.com</t>
+  </si>
+  <si>
+    <t>이승주</t>
+  </si>
+  <si>
+    <t>zouyuanyuan0101@gmail.com</t>
+  </si>
+  <si>
+    <t>문화산업</t>
+  </si>
+  <si>
+    <t>ZOU YUANYUAN</t>
+  </si>
+  <si>
+    <t>fnaf0039@gmail.com</t>
+  </si>
+  <si>
+    <t>박건도</t>
+  </si>
+  <si>
+    <t>nmi123nmi0212@gmail.com</t>
+  </si>
+  <si>
+    <t>노현주</t>
+  </si>
+  <si>
+    <t>kijoopark12@gmail.com</t>
+  </si>
+  <si>
+    <t>박기주</t>
+  </si>
+  <si>
+    <t>crescent0221@naver.com</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>오상현</t>
+  </si>
+  <si>
+    <t>wbslqj0240@naver.com</t>
+  </si>
+  <si>
+    <t>박도은</t>
+  </si>
+  <si>
+    <t>djun321@naver.com</t>
+  </si>
+  <si>
+    <t>황동준</t>
+  </si>
+  <si>
+    <t>alex1874@naver.com</t>
+  </si>
+  <si>
+    <t>김진수</t>
+  </si>
+  <si>
+    <t>cbd12089@naver.com</t>
+  </si>
+  <si>
+    <t>김유경</t>
+  </si>
+  <si>
+    <t>kykim0117@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체전공</t>
+  </si>
+  <si>
+    <t>김규연</t>
+  </si>
+  <si>
+    <t>yuchan0829@naver.com</t>
+  </si>
+  <si>
+    <t>정유찬</t>
+  </si>
+  <si>
+    <t>hallym20246626@gmail.com</t>
+  </si>
+  <si>
+    <t>백송헌</t>
+  </si>
+  <si>
+    <t>dojunc1@gmail.com</t>
+  </si>
+  <si>
+    <t>차도준</t>
+  </si>
+  <si>
+    <t>kay202801@naver.com</t>
+  </si>
+  <si>
+    <t>김아영</t>
+  </si>
+  <si>
+    <t>gnsh2005@naver.com</t>
+  </si>
+  <si>
+    <t>이지나</t>
+  </si>
+  <si>
+    <t>hey.seokjae@gmail.com</t>
+  </si>
+  <si>
+    <t>황석재</t>
+  </si>
+  <si>
+    <t>siyeon050217@gmail.com</t>
+  </si>
+  <si>
+    <t>이시연</t>
+  </si>
+  <si>
+    <t>dldmstj1027@gmail.com</t>
+  </si>
+  <si>
+    <t>roytoy151827@gmail.com</t>
+  </si>
+  <si>
+    <t>김용한</t>
+  </si>
+  <si>
+    <t>tkdahr022@naver.com</t>
+  </si>
+  <si>
+    <t>길상목</t>
+  </si>
+  <si>
+    <t>minchan6020@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">김민찬 </t>
+  </si>
+  <si>
+    <t>minseo1416@naver.com</t>
+  </si>
+  <si>
+    <t>권민서</t>
+  </si>
+  <si>
+    <t>pohang0209@gmail.com</t>
+  </si>
+  <si>
+    <t>이성희</t>
+  </si>
+  <si>
+    <t>yuri060314@naver.com</t>
+  </si>
+  <si>
+    <t>정유리</t>
   </si>
 </sst>
 </file>
@@ -3695,7 +4178,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K500" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:K582" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -19906,35 +20389,2659 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="20">
+      <c r="A500" s="16">
         <v>45731.974920451394</v>
       </c>
-      <c r="B500" s="21" t="s">
+      <c r="B500" s="17" t="s">
         <v>1122</v>
       </c>
-      <c r="C500" s="21" t="s">
+      <c r="C500" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="D500" s="21">
+      <c r="D500" s="17">
         <v>2.0241012E7</v>
       </c>
-      <c r="E500" s="21" t="s">
+      <c r="E500" s="17" t="s">
         <v>971</v>
       </c>
-      <c r="F500" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G500" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H500" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I500" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="J500" s="21" t="s">
+      <c r="F500" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G500" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H500" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I500" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J500" s="17" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="14">
+        <v>45731.98710949074</v>
+      </c>
+      <c r="B501" s="15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C501" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D501" s="15">
+        <v>2.0216712E7</v>
+      </c>
+      <c r="E501" s="15" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F501" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G501" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H501" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I501" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K501" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="16">
+        <v>45732.01551774306</v>
+      </c>
+      <c r="B502" s="17" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C502" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D502" s="17">
+        <v>2.0172727E7</v>
+      </c>
+      <c r="E502" s="17" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F502" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G502" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H502" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I502" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K502" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="14">
+        <v>45732.0459156713</v>
+      </c>
+      <c r="B503" s="15" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C503" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D503" s="15">
+        <v>2.0243035E7</v>
+      </c>
+      <c r="E503" s="15" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F503" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G503" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H503" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I503" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J503" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="16">
+        <v>45732.0809621875</v>
+      </c>
+      <c r="B504" s="17" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C504" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D504" s="17">
+        <v>2.0232722E7</v>
+      </c>
+      <c r="E504" s="17" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F504" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G504" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H504" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I504" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J504" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="14">
+        <v>45732.279086689814</v>
+      </c>
+      <c r="B505" s="15" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C505" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="D505" s="15">
+        <v>2.0195226E7</v>
+      </c>
+      <c r="E505" s="15" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F505" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G505" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H505" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I505" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K505" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="16">
+        <v>45732.4545878125</v>
+      </c>
+      <c r="B506" s="17" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C506" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D506" s="17">
+        <v>2.0246703E7</v>
+      </c>
+      <c r="E506" s="17" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F506" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G506" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H506" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I506" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K506" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="14">
+        <v>45732.454847037036</v>
+      </c>
+      <c r="B507" s="15" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C507" s="15" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D507" s="15">
+        <v>2.0213228E7</v>
+      </c>
+      <c r="E507" s="15" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F507" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G507" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H507" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I507" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K507" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="16">
+        <v>45732.47151351852</v>
+      </c>
+      <c r="B508" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C508" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D508" s="17">
+        <v>2.0226614E7</v>
+      </c>
+      <c r="E508" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F508" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G508" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H508" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I508" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J508" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="14">
+        <v>45732.49680013889</v>
+      </c>
+      <c r="B509" s="15" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C509" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D509" s="15">
+        <v>2.0246208E7</v>
+      </c>
+      <c r="E509" s="15" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F509" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G509" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H509" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I509" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J509" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="16">
+        <v>45732.533115185186</v>
+      </c>
+      <c r="B510" s="17" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C510" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="D510" s="17">
+        <v>2.0241726E7</v>
+      </c>
+      <c r="E510" s="17" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F510" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G510" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H510" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I510" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K510" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="14">
+        <v>45732.55230628472</v>
+      </c>
+      <c r="B511" s="15" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C511" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D511" s="15">
+        <v>2.0241085E7</v>
+      </c>
+      <c r="E511" s="15" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F511" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G511" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H511" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I511" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K511" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="16">
+        <v>45732.55881890046</v>
+      </c>
+      <c r="B512" s="17" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C512" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D512" s="17">
+        <v>2.025384E7</v>
+      </c>
+      <c r="E512" s="17" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F512" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G512" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H512" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I512" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J512" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="14">
+        <v>45732.56030332176</v>
+      </c>
+      <c r="B513" s="15" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C513" s="15" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D513" s="15">
+        <v>2.0202939E7</v>
+      </c>
+      <c r="E513" s="15" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F513" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G513" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H513" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I513" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J513" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="16">
+        <v>45732.571732013894</v>
+      </c>
+      <c r="B514" s="17" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C514" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D514" s="17">
+        <v>2.0246236E7</v>
+      </c>
+      <c r="E514" s="17" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F514" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G514" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H514" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I514" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J514" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="14">
+        <v>45732.59306328704</v>
+      </c>
+      <c r="B515" s="15" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C515" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D515" s="15">
+        <v>2.021302E7</v>
+      </c>
+      <c r="E515" s="15" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F515" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G515" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H515" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I515" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J515" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="16">
+        <v>45732.59506907407</v>
+      </c>
+      <c r="B516" s="17" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C516" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D516" s="17">
+        <v>2.0222222E7</v>
+      </c>
+      <c r="E516" s="17" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F516" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G516" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H516" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I516" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J516" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="14">
+        <v>45732.600234618054</v>
+      </c>
+      <c r="B517" s="15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C517" s="15" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D517" s="15">
+        <v>2.0246606E7</v>
+      </c>
+      <c r="E517" s="15" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F517" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G517" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H517" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I517" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J517" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="16">
+        <v>45732.60869972222</v>
+      </c>
+      <c r="B518" s="17" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C518" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="D518" s="17">
+        <v>2.0235218E7</v>
+      </c>
+      <c r="E518" s="17" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F518" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G518" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H518" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I518" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K518" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="14">
+        <v>45732.609036388894</v>
+      </c>
+      <c r="B519" s="15" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C519" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D519" s="15">
+        <v>2.024255E7</v>
+      </c>
+      <c r="E519" s="15" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F519" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G519" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H519" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I519" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J519" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="16">
+        <v>45732.61425615741</v>
+      </c>
+      <c r="B520" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C520" s="17" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D520" s="17">
+        <v>2.0227042E7</v>
+      </c>
+      <c r="E520" s="17" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F520" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G520" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H520" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I520" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K520" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="14">
+        <v>45732.615584328705</v>
+      </c>
+      <c r="B521" s="15" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C521" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D521" s="15">
+        <v>2.0202514E7</v>
+      </c>
+      <c r="E521" s="15" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F521" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G521" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H521" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I521" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J521" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="16">
+        <v>45732.617588113426</v>
+      </c>
+      <c r="B522" s="17" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C522" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D522" s="17">
+        <v>2.0242949E7</v>
+      </c>
+      <c r="E522" s="17" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F522" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G522" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H522" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I522" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J522" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="14">
+        <v>45732.62568158565</v>
+      </c>
+      <c r="B523" s="15" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C523" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="D523" s="15">
+        <v>2.0207106E7</v>
+      </c>
+      <c r="E523" s="15" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F523" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G523" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H523" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I523" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J523" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="16">
+        <v>45732.63664059028</v>
+      </c>
+      <c r="B524" s="17" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C524" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="D524" s="17">
+        <v>2.0191702E7</v>
+      </c>
+      <c r="E524" s="17" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F524" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G524" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H524" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I524" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J524" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="14">
+        <v>45732.63802549768</v>
+      </c>
+      <c r="B525" s="15" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C525" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D525" s="15">
+        <v>2.0255273E7</v>
+      </c>
+      <c r="E525" s="15" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F525" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G525" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H525" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I525" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J525" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="16">
+        <v>45732.64155606482</v>
+      </c>
+      <c r="B526" s="17" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C526" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="D526" s="17">
+        <v>2.020516E7</v>
+      </c>
+      <c r="E526" s="17" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F526" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G526" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H526" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I526" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K526" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="14">
+        <v>45732.654351875</v>
+      </c>
+      <c r="B527" s="15" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C527" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D527" s="15">
+        <v>2.0232949E7</v>
+      </c>
+      <c r="E527" s="15" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F527" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G527" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H527" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I527" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J527" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="16">
+        <v>45732.65461341436</v>
+      </c>
+      <c r="B528" s="17" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C528" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D528" s="17">
+        <v>2.0242214E7</v>
+      </c>
+      <c r="E528" s="17" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F528" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G528" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H528" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I528" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J528" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="14">
+        <v>45732.65626043981</v>
+      </c>
+      <c r="B529" s="15" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C529" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D529" s="15">
+        <v>2.0215238E7</v>
+      </c>
+      <c r="E529" s="15" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F529" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G529" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H529" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I529" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J529" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="16">
+        <v>45732.66827106482</v>
+      </c>
+      <c r="B530" s="17" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C530" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D530" s="17">
+        <v>2.0243533E7</v>
+      </c>
+      <c r="E530" s="17" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F530" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G530" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H530" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I530" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J530" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="14">
+        <v>45732.67782986111</v>
+      </c>
+      <c r="B531" s="15" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C531" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D531" s="15">
+        <v>2.0243818E7</v>
+      </c>
+      <c r="E531" s="15" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F531" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G531" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H531" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I531" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K531" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="16">
+        <v>45732.69093128473</v>
+      </c>
+      <c r="B532" s="17" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C532" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D532" s="17">
+        <v>2.0245223E7</v>
+      </c>
+      <c r="E532" s="17" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F532" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G532" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H532" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I532" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J532" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="14">
+        <v>45732.71028119213</v>
+      </c>
+      <c r="B533" s="15" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C533" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D533" s="15">
+        <v>2.0241235E7</v>
+      </c>
+      <c r="E533" s="15" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F533" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G533" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H533" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I533" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K533" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="16">
+        <v>45732.73759225695</v>
+      </c>
+      <c r="B534" s="17" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C534" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D534" s="17">
+        <v>2.0253244E7</v>
+      </c>
+      <c r="E534" s="17" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F534" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G534" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H534" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I534" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J534" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="14">
+        <v>45732.73760429399</v>
+      </c>
+      <c r="B535" s="15" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C535" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="D535" s="15">
+        <v>2.0215255E7</v>
+      </c>
+      <c r="E535" s="15" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F535" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G535" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H535" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I535" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J535" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="16">
+        <v>45732.7477999074</v>
+      </c>
+      <c r="B536" s="17" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C536" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="D536" s="17">
+        <v>2.0246627E7</v>
+      </c>
+      <c r="E536" s="17" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F536" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G536" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H536" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I536" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J536" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="14">
+        <v>45732.78358216435</v>
+      </c>
+      <c r="B537" s="15" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C537" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="D537" s="15">
+        <v>2.0203308E7</v>
+      </c>
+      <c r="E537" s="15" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F537" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G537" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H537" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I537" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J537" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="16">
+        <v>45732.784535370374</v>
+      </c>
+      <c r="B538" s="17" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C538" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D538" s="17">
+        <v>2.0243906E7</v>
+      </c>
+      <c r="E538" s="17" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F538" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G538" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H538" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I538" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J538" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="14">
+        <v>45732.786464652774</v>
+      </c>
+      <c r="B539" s="15" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C539" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D539" s="15">
+        <v>2.0231212E7</v>
+      </c>
+      <c r="E539" s="15" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F539" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G539" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H539" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I539" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K539" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="16">
+        <v>45732.78830107639</v>
+      </c>
+      <c r="B540" s="17" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C540" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="D540" s="17">
+        <v>2.0242566E7</v>
+      </c>
+      <c r="E540" s="17" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F540" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G540" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H540" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I540" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K540" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="14">
+        <v>45732.7884752199</v>
+      </c>
+      <c r="B541" s="15" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C541" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="D541" s="15">
+        <v>2.0242516E7</v>
+      </c>
+      <c r="E541" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="F541" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G541" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H541" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I541" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K541" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="16">
+        <v>45732.78908231482</v>
+      </c>
+      <c r="B542" s="17" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C542" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D542" s="17">
+        <v>2.0242537E7</v>
+      </c>
+      <c r="E542" s="17" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F542" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G542" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H542" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I542" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J542" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="14">
+        <v>45732.80093900463</v>
+      </c>
+      <c r="B543" s="15" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C543" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D543" s="15">
+        <v>2.0212105E7</v>
+      </c>
+      <c r="E543" s="15" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F543" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G543" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H543" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I543" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K543" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="16">
+        <v>45732.807524178235</v>
+      </c>
+      <c r="B544" s="17" t="s">
+        <v>715</v>
+      </c>
+      <c r="C544" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D544" s="17">
+        <v>2.0242917E7</v>
+      </c>
+      <c r="E544" s="17" t="s">
+        <v>716</v>
+      </c>
+      <c r="F544" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G544" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H544" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I544" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J544" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="14">
+        <v>45732.807656585646</v>
+      </c>
+      <c r="B545" s="15" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C545" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D545" s="15">
+        <v>2.0232135E7</v>
+      </c>
+      <c r="E545" s="15" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F545" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G545" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H545" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I545" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K545" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="16">
+        <v>45732.80832456019</v>
+      </c>
+      <c r="B546" s="17" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C546" s="17" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D546" s="17">
+        <v>2.0212503E7</v>
+      </c>
+      <c r="E546" s="17" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F546" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G546" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H546" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I546" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J546" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="14">
+        <v>45732.81481038194</v>
+      </c>
+      <c r="B547" s="15" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C547" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="D547" s="15">
+        <v>2.0242315E7</v>
+      </c>
+      <c r="E547" s="15" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F547" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G547" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H547" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I547" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J547" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="16">
+        <v>45732.82066082176</v>
+      </c>
+      <c r="B548" s="17" t="s">
+        <v>761</v>
+      </c>
+      <c r="C548" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D548" s="17">
+        <v>2.0243023E7</v>
+      </c>
+      <c r="E548" s="17" t="s">
+        <v>762</v>
+      </c>
+      <c r="F548" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G548" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H548" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I548" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K548" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="14">
+        <v>45732.82088637732</v>
+      </c>
+      <c r="B549" s="15" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C549" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D549" s="15">
+        <v>2.0242585E7</v>
+      </c>
+      <c r="E549" s="15" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F549" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G549" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H549" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I549" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J549" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="16">
+        <v>45732.8210721875</v>
+      </c>
+      <c r="B550" s="17" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C550" s="17" t="s">
+        <v>643</v>
+      </c>
+      <c r="D550" s="17">
+        <v>2.0221108E7</v>
+      </c>
+      <c r="E550" s="17" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F550" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G550" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H550" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I550" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J550" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="14">
+        <v>45732.82417673611</v>
+      </c>
+      <c r="B551" s="15" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C551" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D551" s="15">
+        <v>2.020513E7</v>
+      </c>
+      <c r="E551" s="15" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F551" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G551" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H551" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I551" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J551" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="16">
+        <v>45732.82503420139</v>
+      </c>
+      <c r="B552" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="C552" s="17" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D552" s="17">
+        <v>2.0241232E7</v>
+      </c>
+      <c r="E552" s="17" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F552" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G552" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H552" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I552" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J552" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="14">
+        <v>45732.825605983795</v>
+      </c>
+      <c r="B553" s="15" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C553" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D553" s="15">
+        <v>2.0243841E7</v>
+      </c>
+      <c r="E553" s="15" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F553" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G553" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H553" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I553" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K553" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="16">
+        <v>45732.82564105324</v>
+      </c>
+      <c r="B554" s="17" t="s">
+        <v>623</v>
+      </c>
+      <c r="C554" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="D554" s="17">
+        <v>2.0256637E7</v>
+      </c>
+      <c r="E554" s="17" t="s">
+        <v>624</v>
+      </c>
+      <c r="F554" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G554" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H554" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I554" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K554" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="14">
+        <v>45732.829404930555</v>
+      </c>
+      <c r="B555" s="15" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C555" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D555" s="15">
+        <v>2.0202531E7</v>
+      </c>
+      <c r="E555" s="15" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F555" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G555" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H555" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I555" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J555" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="16">
+        <v>45732.82941019676</v>
+      </c>
+      <c r="B556" s="17" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C556" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D556" s="17">
+        <v>2.0223501E7</v>
+      </c>
+      <c r="E556" s="17" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F556" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G556" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H556" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I556" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K556" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="14">
+        <v>45732.830663773144</v>
+      </c>
+      <c r="B557" s="15" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C557" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="D557" s="15">
+        <v>2.0202348E7</v>
+      </c>
+      <c r="E557" s="15" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F557" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G557" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H557" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I557" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K557" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="16">
+        <v>45732.83338273148</v>
+      </c>
+      <c r="B558" s="17" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C558" s="17" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D558" s="17">
+        <v>2.0218005E7</v>
+      </c>
+      <c r="E558" s="17" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F558" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G558" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H558" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I558" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K558" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="14">
+        <v>45732.83603207176</v>
+      </c>
+      <c r="B559" s="15" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C559" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D559" s="15">
+        <v>2.0241611E7</v>
+      </c>
+      <c r="E559" s="15" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F559" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G559" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H559" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I559" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K559" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="16">
+        <v>45732.83809914352</v>
+      </c>
+      <c r="B560" s="17" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C560" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="D560" s="17">
+        <v>2.0215152E7</v>
+      </c>
+      <c r="E560" s="17" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F560" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G560" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H560" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I560" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J560" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="14">
+        <v>45732.83998123843</v>
+      </c>
+      <c r="B561" s="15" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C561" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="D561" s="15">
+        <v>2.0212527E7</v>
+      </c>
+      <c r="E561" s="15" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F561" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G561" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H561" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I561" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K561" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="16">
+        <v>45732.84157950232</v>
+      </c>
+      <c r="B562" s="17" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C562" s="17" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D562" s="17">
+        <v>2.020162E7</v>
+      </c>
+      <c r="E562" s="17" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F562" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G562" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H562" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I562" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J562" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="14">
+        <v>45732.846044606486</v>
+      </c>
+      <c r="B563" s="15" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C563" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D563" s="15">
+        <v>2.0206612E7</v>
+      </c>
+      <c r="E563" s="15" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F563" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G563" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H563" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I563" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K563" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="16">
+        <v>45732.84778497685</v>
+      </c>
+      <c r="B564" s="17" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C564" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D564" s="17">
+        <v>2.0183016E7</v>
+      </c>
+      <c r="E564" s="17" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F564" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G564" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H564" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I564" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K564" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="14">
+        <v>45732.85046543981</v>
+      </c>
+      <c r="B565" s="15" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C565" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="D565" s="15">
+        <v>2.0233214E7</v>
+      </c>
+      <c r="E565" s="15" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F565" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G565" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H565" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I565" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J565" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="16">
+        <v>45732.85347777778</v>
+      </c>
+      <c r="B566" s="17" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C566" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D566" s="17">
+        <v>2.0241018E7</v>
+      </c>
+      <c r="E566" s="17" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F566" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G566" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H566" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I566" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K566" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="14">
+        <v>45732.85378337963</v>
+      </c>
+      <c r="B567" s="15" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C567" s="15" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D567" s="15">
+        <v>2.0243303E7</v>
+      </c>
+      <c r="E567" s="15" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F567" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G567" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H567" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I567" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K567" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="16">
+        <v>45732.85557363426</v>
+      </c>
+      <c r="B568" s="17" t="s">
+        <v>645</v>
+      </c>
+      <c r="C568" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D568" s="17">
+        <v>2.0223044E7</v>
+      </c>
+      <c r="E568" s="17" t="s">
+        <v>646</v>
+      </c>
+      <c r="F568" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G568" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H568" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I568" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J568" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="14">
+        <v>45732.86675905093</v>
+      </c>
+      <c r="B569" s="15" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C569" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D569" s="15">
+        <v>2.0241091E7</v>
+      </c>
+      <c r="E569" s="15" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F569" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G569" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H569" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I569" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J569" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="16">
+        <v>45732.86844155093</v>
+      </c>
+      <c r="B570" s="17" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C570" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="D570" s="17">
+        <v>2.0246626E7</v>
+      </c>
+      <c r="E570" s="17" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F570" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G570" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H570" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I570" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K570" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="14">
+        <v>45732.87130976852</v>
+      </c>
+      <c r="B571" s="15" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C571" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D571" s="15">
+        <v>2.0245268E7</v>
+      </c>
+      <c r="E571" s="15" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F571" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G571" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H571" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I571" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J571" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="16">
+        <v>45732.87230777778</v>
+      </c>
+      <c r="B572" s="17" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C572" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D572" s="17">
+        <v>2.020161E7</v>
+      </c>
+      <c r="E572" s="17" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F572" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G572" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H572" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I572" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J572" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="14">
+        <v>45732.877371215276</v>
+      </c>
+      <c r="B573" s="15" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C573" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D573" s="15">
+        <v>2.024627E7</v>
+      </c>
+      <c r="E573" s="15" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F573" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G573" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H573" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I573" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J573" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="16">
+        <v>45732.87962921296</v>
+      </c>
+      <c r="B574" s="17" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C574" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D574" s="17">
+        <v>2.0212763E7</v>
+      </c>
+      <c r="E574" s="17" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F574" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G574" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H574" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I574" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J574" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="14">
+        <v>45732.88123792824</v>
+      </c>
+      <c r="B575" s="15" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C575" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D575" s="15">
+        <v>2.0243531E7</v>
+      </c>
+      <c r="E575" s="15" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F575" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G575" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H575" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I575" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K575" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="16">
+        <v>45732.88965527777</v>
+      </c>
+      <c r="B576" s="17" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C576" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D576" s="17">
+        <v>2.0232128E7</v>
+      </c>
+      <c r="E576" s="17" t="s">
+        <v>795</v>
+      </c>
+      <c r="F576" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G576" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H576" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I576" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K576" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="14">
+        <v>45732.89191142361</v>
+      </c>
+      <c r="B577" s="15" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C577" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D577" s="15">
+        <v>2.0202927E7</v>
+      </c>
+      <c r="E577" s="15" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F577" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G577" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H577" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I577" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K577" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="16">
+        <v>45732.89582340278</v>
+      </c>
+      <c r="B578" s="17" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C578" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D578" s="17">
+        <v>2.0217124E7</v>
+      </c>
+      <c r="E578" s="17" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F578" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G578" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H578" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I578" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J578" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="14">
+        <v>45732.91138304398</v>
+      </c>
+      <c r="B579" s="15" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C579" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D579" s="15">
+        <v>2.0242508E7</v>
+      </c>
+      <c r="E579" s="15" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F579" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G579" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H579" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I579" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K579" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="16">
+        <v>45732.913649062495</v>
+      </c>
+      <c r="B580" s="17" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C580" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D580" s="17">
+        <v>2.0201603E7</v>
+      </c>
+      <c r="E580" s="17" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F580" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G580" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H580" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I580" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K580" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="14">
+        <v>45732.915505983794</v>
+      </c>
+      <c r="B581" s="15" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C581" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D581" s="15">
+        <v>2.0222999E7</v>
+      </c>
+      <c r="E581" s="15" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F581" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G581" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H581" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I581" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K581" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="20">
+        <v>45732.91616121528</v>
+      </c>
+      <c r="B582" s="21" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C582" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D582" s="21">
+        <v>2.0253725E7</v>
+      </c>
+      <c r="E582" s="21" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F582" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G582" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H582" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="I582" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J582" s="21" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
